--- a/docs/00_构建与版本/故障码/LTD内部技术与治理资料.xlsx
+++ b/docs/00_构建与版本/故障码/LTD内部技术与治理资料.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="故障代码技术表" sheetId="1" r:id="R025c8cf83528436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元本机故障" sheetId="2" r:id="Rc54d08dc0ade405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主控单元参数原表" sheetId="3" r:id="Rc6abc4a22247413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主控单元结果原表" sheetId="4" r:id="Ra37a22e8a1fe4b4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元参数原表" sheetId="5" r:id="R364b3b2ff7c947dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元结果原表" sheetId="6" r:id="R9860808a980e45cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示寄存器映射" sheetId="7" r:id="Rd23a79838dc94c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数元数据" sheetId="8" r:id="R13ee740a6c7b4e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类规则" sheetId="9" r:id="Re8433d75d7f14d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链路复查" sheetId="10" r:id="Rb89490a39ebb4836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="治理摘要" sheetId="11" r:id="Rfb1e27042a9145ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表差异" sheetId="12" r:id="R8c3999b971794dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3阶段评审" sheetId="13" r:id="Rf59103852311467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3.2日志清单" sheetId="14" r:id="R025501df21984462"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编号迁移" sheetId="15" r:id="Rda2346bce68542d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="故障代码技术表" sheetId="1" r:id="Reb8482535c5849d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元本机故障" sheetId="2" r:id="R0e4a6d72c22a4883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主控单元参数原表" sheetId="3" r:id="R6a1d6e7e18d64b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主控单元结果原表" sheetId="4" r:id="Re37973d3c94e4d48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元参数原表" sheetId="5" r:id="R9c466b52f2f94728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示单元结果原表" sheetId="6" r:id="R36995c0b32c94663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="显示寄存器映射" sheetId="7" r:id="R9c2d0e6f7e4b4bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数元数据" sheetId="8" r:id="Rd32c8a8d76e34cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类规则" sheetId="9" r:id="R64a04ab682044ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链路复查" sheetId="10" r:id="Rc8b26ad873224db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="治理摘要" sheetId="11" r:id="R7c0e9a86988945a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表差异" sheetId="12" r:id="R0866e9c663464d61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3阶段评审" sheetId="13" r:id="R23ed1151e10d45aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3.2日志清单" sheetId="14" r:id="R3c16ef86bd844442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编号迁移" sheetId="15" r:id="R61b564d4482448c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,7 +337,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="100">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -604,6 +604,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1029,25 +1032,25 @@
         <x:v>1-2 电机通讯错误</x:v>
       </x:c>
       <x:c r="O4" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P4"/>
     </x:row>
     <x:row r="5" ht="94" customHeight="1">
       <x:c r="A5" s="74" t="str">
-        <x:v>11-4</x:v>
+        <x:v>11-3</x:v>
       </x:c>
       <x:c r="B5" s="74" t="str">
-        <x:v>0x000B0004</x:v>
+        <x:v>0x000B0003</x:v>
       </x:c>
       <x:c r="C5" s="72" t="str">
-        <x:v>MOTOR_DISABLED</x:v>
+        <x:v>MOTOR_TMC_CONFIG_LOST</x:v>
       </x:c>
       <x:c r="D5" s="74" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="E5" s="74" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="72" t="str">
         <x:v>电机驱动</x:v>
@@ -1056,326 +1059,21 @@
         <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="H5" s="72" t="str">
-        <x:v>电机驱动未使能</x:v>
+        <x:v>电机驱动配置丢失</x:v>
       </x:c>
       <x:c r="I5" s="72" t="str">
-        <x:v>电机驱动输出未使能</x:v>
+        <x:v>TMC5130运行期复位或关键配置丢失</x:v>
       </x:c>
       <x:c r="J5" s="72" t="str">
-        <x:v>电机驱动未使能</x:v>
+        <x:v>电机驱动配置丢失</x:v>
       </x:c>
       <x:c r="K5" s="74" t="str">
         <x:v>使用中</x:v>
       </x:c>
       <x:c r="L5" s="74" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M5" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:48
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:70
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1071
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1075
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_driver_param.c:162</x:v>
-      </x:c>
-      <x:c r="N5" s="72" t="str">
-        <x:v>1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
-      </x:c>
-      <x:c r="O5" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P5"/>
-    </x:row>
-    <x:row r="6" ht="63" customHeight="1">
-      <x:c r="A6" s="73" t="str">
-        <x:v>11-5</x:v>
-      </x:c>
-      <x:c r="B6" s="73" t="str">
-        <x:v>0x000B0005</x:v>
-      </x:c>
-      <x:c r="C6" s="68" t="str">
-        <x:v>MOTOR_UNKNOWN_FEEDBACK</x:v>
-      </x:c>
-      <x:c r="D6" s="73" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E6" s="73" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G6" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H6" s="68" t="str">
-        <x:v>电机反馈未知</x:v>
-      </x:c>
-      <x:c r="I6" s="68" t="str">
-        <x:v>电机反馈状态无法识别</x:v>
-      </x:c>
-      <x:c r="J6" s="68" t="str">
-        <x:v>电机反馈未知</x:v>
-      </x:c>
-      <x:c r="K6" s="73" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L6" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M6" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:70
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:964</x:v>
-      </x:c>
-      <x:c r="N6" s="68" t="str">
-        <x:v>1-5 电机状态异常</x:v>
-      </x:c>
-      <x:c r="O6" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P6"/>
-    </x:row>
-    <x:row r="7" ht="94" customHeight="1">
-      <x:c r="A7" s="74" t="str">
-        <x:v>11-10</x:v>
-      </x:c>
-      <x:c r="B7" s="74" t="str">
-        <x:v>0x000B000A</x:v>
-      </x:c>
-      <x:c r="C7" s="72" t="str">
-        <x:v>MOTOR_STEP_ERROR</x:v>
-      </x:c>
-      <x:c r="D7" s="74" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E7" s="74" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G7" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H7" s="72" t="str">
-        <x:v>电机无有效位移</x:v>
-      </x:c>
-      <x:c r="I7" s="72" t="str">
-        <x:v>丢步检测</x:v>
-      </x:c>
-      <x:c r="J7" s="72" t="str">
-        <x:v>电机无有效位移</x:v>
-      </x:c>
-      <x:c r="K7" s="74" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L7" s="74" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M7" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1108
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1111
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1122
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2024</x:v>
-      </x:c>
-      <x:c r="N7" s="72" t="str">
-        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
-      </x:c>
-      <x:c r="O7" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P7"/>
-    </x:row>
-    <x:row r="8" ht="78" customHeight="1">
-      <x:c r="A8" s="73" t="str">
-        <x:v>11-16</x:v>
-      </x:c>
-      <x:c r="B8" s="73" t="str">
-        <x:v>0x000B0010</x:v>
-      </x:c>
-      <x:c r="C8" s="68" t="str">
-        <x:v>MOTOR_CHARGE_PUMP_UNDER_VOLTAGE</x:v>
-      </x:c>
-      <x:c r="D8" s="73" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E8" s="73" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F8" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G8" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H8" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
-      </x:c>
-      <x:c r="I8" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
-      </x:c>
-      <x:c r="J8" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
-      </x:c>
-      <x:c r="K8" s="73" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L8" s="73" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M8" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:47
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:69
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:998</x:v>
-      </x:c>
-      <x:c r="N8" s="68" t="str">
-        <x:v>1-7 电机驱动器报警</x:v>
-      </x:c>
-      <x:c r="O8" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P8"/>
-    </x:row>
-    <x:row r="9" ht="78" customHeight="1">
-      <x:c r="A9" s="74" t="str">
-        <x:v>11-17</x:v>
-      </x:c>
-      <x:c r="B9" s="74" t="str">
-        <x:v>0x000B0011</x:v>
-      </x:c>
-      <x:c r="C9" s="72" t="str">
-        <x:v>MOTOR_OVERTEMPERATURE</x:v>
-      </x:c>
-      <x:c r="D9" s="74" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E9" s="74" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G9" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H9" s="72" t="str">
-        <x:v>电机驱动过温关断</x:v>
-      </x:c>
-      <x:c r="I9" s="72" t="str">
-        <x:v>电机驱动已过温关断</x:v>
-      </x:c>
-      <x:c r="J9" s="72" t="str">
-        <x:v>电机驱动过温停止</x:v>
-      </x:c>
-      <x:c r="K9" s="74" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L9" s="74" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M9" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:71
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:101
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:142</x:v>
-      </x:c>
-      <x:c r="N9" s="72" t="str">
-        <x:v>1-7 电机驱动器报警</x:v>
-      </x:c>
-      <x:c r="O9" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P9"/>
-    </x:row>
-    <x:row r="10" ht="94" customHeight="1">
-      <x:c r="A10" s="73" t="str">
-        <x:v>11-18</x:v>
-      </x:c>
-      <x:c r="B10" s="73" t="str">
-        <x:v>0x000B0012</x:v>
-      </x:c>
-      <x:c r="C10" s="68" t="str">
-        <x:v>MOTOR_RUN_TIMEOUT</x:v>
-      </x:c>
-      <x:c r="D10" s="73" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E10" s="73" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F10" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G10" s="68" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H10" s="68" t="str">
-        <x:v>电机运行超时</x:v>
-      </x:c>
-      <x:c r="I10" s="68" t="str">
-        <x:v>电机整段运行超时</x:v>
-      </x:c>
-      <x:c r="J10" s="68" t="str">
-        <x:v>电机运行超时</x:v>
-      </x:c>
-      <x:c r="K10" s="73" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L10" s="73" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="M10" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:50
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:72
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2028
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2352
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2355
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2362</x:v>
-      </x:c>
-      <x:c r="N10" s="68" t="str">
-        <x:v>1-10 输入步进数错误</x:v>
-      </x:c>
-      <x:c r="O10" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P10"/>
-    </x:row>
-    <x:row r="11" ht="94" customHeight="1">
-      <x:c r="A11" s="74" t="str">
-        <x:v>11-19</x:v>
-      </x:c>
-      <x:c r="B11" s="74" t="str">
-        <x:v>0x000B0013</x:v>
-      </x:c>
-      <x:c r="C11" s="72" t="str">
-        <x:v>MOTOR_TMC_CONFIG_LOST</x:v>
-      </x:c>
-      <x:c r="D11" s="74" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E11" s="74" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F11" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="G11" s="72" t="str">
-        <x:v>电机驱动</x:v>
-      </x:c>
-      <x:c r="H11" s="72" t="str">
-        <x:v>电机驱动配置丢失</x:v>
-      </x:c>
-      <x:c r="I11" s="72" t="str">
-        <x:v>TMC5130运行期复位或关键配置丢失</x:v>
-      </x:c>
-      <x:c r="J11" s="72" t="str">
-        <x:v>电机驱动配置丢失</x:v>
-      </x:c>
-      <x:c r="K11" s="74" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L11" s="74" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="M11" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/fault_manager.c:68
 LTD_MAIN_CPU2/Application/Src/fault_recovery.c:46
 LTD_MAIN_CPU2/Application/Src/measure_zero.c:68
@@ -1384,70 +1082,375 @@
 LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1021
 LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1028</x:v>
       </x:c>
-      <x:c r="N11" s="72" t="str">
+      <x:c r="N5" s="72" t="str">
         <x:v>1-3 电机驱动异常重启</x:v>
       </x:c>
-      <x:c r="O11" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P11"/>
-    </x:row>
-    <x:row r="12" ht="78" customHeight="1">
-      <x:c r="A12" s="73" t="str">
-        <x:v>11-20</x:v>
-      </x:c>
-      <x:c r="B12" s="73" t="str">
-        <x:v>0x000B0014</x:v>
-      </x:c>
-      <x:c r="C12" s="68" t="str">
+      <x:c r="O5" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P5"/>
+    </x:row>
+    <x:row r="6" ht="63" customHeight="1">
+      <x:c r="A6" s="73" t="str">
+        <x:v>11-4</x:v>
+      </x:c>
+      <x:c r="B6" s="73" t="str">
+        <x:v>0x000B0004</x:v>
+      </x:c>
+      <x:c r="C6" s="68" t="str">
+        <x:v>MOTOR_DISABLED</x:v>
+      </x:c>
+      <x:c r="D6" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E6" s="73" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F6" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G6" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H6" s="68" t="str">
+        <x:v>电机驱动未使能</x:v>
+      </x:c>
+      <x:c r="I6" s="68" t="str">
+        <x:v>电机驱动输出未使能</x:v>
+      </x:c>
+      <x:c r="J6" s="68" t="str">
+        <x:v>电机驱动未使能</x:v>
+      </x:c>
+      <x:c r="K6" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L6" s="73" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M6" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:48
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:70
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1071
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1075
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_driver_param.c:162</x:v>
+      </x:c>
+      <x:c r="N6" s="68" t="str">
+        <x:v>1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
+      </x:c>
+      <x:c r="O6" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P6"/>
+    </x:row>
+    <x:row r="7" ht="94" customHeight="1">
+      <x:c r="A7" s="74" t="str">
+        <x:v>11-5</x:v>
+      </x:c>
+      <x:c r="B7" s="74" t="str">
+        <x:v>0x000B0005</x:v>
+      </x:c>
+      <x:c r="C7" s="72" t="str">
+        <x:v>MOTOR_UNKNOWN_FEEDBACK</x:v>
+      </x:c>
+      <x:c r="D7" s="74" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E7" s="74" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="72" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G7" s="72" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H7" s="72" t="str">
+        <x:v>电机反馈未知</x:v>
+      </x:c>
+      <x:c r="I7" s="72" t="str">
+        <x:v>电机反馈状态无法识别</x:v>
+      </x:c>
+      <x:c r="J7" s="72" t="str">
+        <x:v>电机反馈未知</x:v>
+      </x:c>
+      <x:c r="K7" s="74" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L7" s="74" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M7" s="72" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:70
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:964</x:v>
+      </x:c>
+      <x:c r="N7" s="72" t="str">
+        <x:v>1-5 电机状态异常</x:v>
+      </x:c>
+      <x:c r="O7" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P7"/>
+    </x:row>
+    <x:row r="8" ht="78" customHeight="1">
+      <x:c r="A8" s="73" t="str">
+        <x:v>11-10</x:v>
+      </x:c>
+      <x:c r="B8" s="73" t="str">
+        <x:v>0x000B000A</x:v>
+      </x:c>
+      <x:c r="C8" s="68" t="str">
+        <x:v>MOTOR_STEP_ERROR</x:v>
+      </x:c>
+      <x:c r="D8" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E8" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G8" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H8" s="68" t="str">
+        <x:v>电机无有效位移</x:v>
+      </x:c>
+      <x:c r="I8" s="68" t="str">
+        <x:v>丢步检测</x:v>
+      </x:c>
+      <x:c r="J8" s="68" t="str">
+        <x:v>电机无有效位移</x:v>
+      </x:c>
+      <x:c r="K8" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L8" s="73" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1108
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1111
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1122
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2024</x:v>
+      </x:c>
+      <x:c r="N8" s="68" t="str">
+        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
+      </x:c>
+      <x:c r="O8" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P8"/>
+    </x:row>
+    <x:row r="9" ht="78" customHeight="1">
+      <x:c r="A9" s="74" t="str">
+        <x:v>11-11</x:v>
+      </x:c>
+      <x:c r="B9" s="74" t="str">
+        <x:v>0x000B000B</x:v>
+      </x:c>
+      <x:c r="C9" s="72" t="str">
         <x:v>MOTOR_STALL_ERROR</x:v>
       </x:c>
-      <x:c r="D12" s="73" t="n">
+      <x:c r="D9" s="74" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E12" s="73" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="68" t="str">
+      <x:c r="E9" s="74" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F9" s="72" t="str">
         <x:v>电机驱动</x:v>
       </x:c>
-      <x:c r="G12" s="68" t="str">
+      <x:c r="G9" s="72" t="str">
         <x:v>电机驱动</x:v>
       </x:c>
-      <x:c r="H12" s="68" t="str">
+      <x:c r="H9" s="72" t="str">
         <x:v>电机堵转</x:v>
       </x:c>
-      <x:c r="I12" s="68" t="str">
+      <x:c r="I9" s="72" t="str">
         <x:v>电机堵转或负载阻力过大</x:v>
       </x:c>
-      <x:c r="J12" s="68" t="str">
+      <x:c r="J9" s="72" t="str">
         <x:v>电机运行阻力大</x:v>
       </x:c>
-      <x:c r="K12" s="73" t="str">
+      <x:c r="K9" s="74" t="str">
         <x:v>使用中</x:v>
       </x:c>
-      <x:c r="L12" s="73" t="n">
+      <x:c r="L9" s="74" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M12" s="68" t="str">
+      <x:c r="M9" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:72
 LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:97
 LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:148</x:v>
       </x:c>
+      <x:c r="N9" s="72" t="str">
+        <x:v>1-11 电机堵转</x:v>
+      </x:c>
+      <x:c r="O9" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P9"/>
+    </x:row>
+    <x:row r="10" ht="94" customHeight="1">
+      <x:c r="A10" s="73" t="str">
+        <x:v>11-16</x:v>
+      </x:c>
+      <x:c r="B10" s="73" t="str">
+        <x:v>0x000B0010</x:v>
+      </x:c>
+      <x:c r="C10" s="68" t="str">
+        <x:v>MOTOR_CHARGE_PUMP_UNDER_VOLTAGE</x:v>
+      </x:c>
+      <x:c r="D10" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E10" s="73" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F10" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G10" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H10" s="68" t="str">
+        <x:v>电荷泵欠压</x:v>
+      </x:c>
+      <x:c r="I10" s="68" t="str">
+        <x:v>电荷泵欠压</x:v>
+      </x:c>
+      <x:c r="J10" s="68" t="str">
+        <x:v>电荷泵欠压</x:v>
+      </x:c>
+      <x:c r="K10" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L10" s="73" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M10" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:47
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:69
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:998</x:v>
+      </x:c>
+      <x:c r="N10" s="68" t="str">
+        <x:v>1-7 电机驱动器报警</x:v>
+      </x:c>
+      <x:c r="O10" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P10"/>
+    </x:row>
+    <x:row r="11" ht="94" customHeight="1">
+      <x:c r="A11" s="74" t="str">
+        <x:v>11-17</x:v>
+      </x:c>
+      <x:c r="B11" s="74" t="str">
+        <x:v>0x000B0011</x:v>
+      </x:c>
+      <x:c r="C11" s="72" t="str">
+        <x:v>MOTOR_OVERTEMPERATURE</x:v>
+      </x:c>
+      <x:c r="D11" s="74" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E11" s="74" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="72" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G11" s="72" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H11" s="72" t="str">
+        <x:v>电机驱动过温关断</x:v>
+      </x:c>
+      <x:c r="I11" s="72" t="str">
+        <x:v>电机驱动已过温关断</x:v>
+      </x:c>
+      <x:c r="J11" s="72" t="str">
+        <x:v>电机驱动过温停止</x:v>
+      </x:c>
+      <x:c r="K11" s="74" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L11" s="74" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M11" s="72" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:71
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:101
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:142</x:v>
+      </x:c>
+      <x:c r="N11" s="72" t="str">
+        <x:v>1-7 电机驱动器报警</x:v>
+      </x:c>
+      <x:c r="O11" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P11"/>
+    </x:row>
+    <x:row r="12" ht="78" customHeight="1">
+      <x:c r="A12" s="73" t="str">
+        <x:v>11-18</x:v>
+      </x:c>
+      <x:c r="B12" s="73" t="str">
+        <x:v>0x000B0012</x:v>
+      </x:c>
+      <x:c r="C12" s="68" t="str">
+        <x:v>MOTOR_RUN_TIMEOUT</x:v>
+      </x:c>
+      <x:c r="D12" s="73" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E12" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F12" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="G12" s="68" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="H12" s="68" t="str">
+        <x:v>电机运行超时</x:v>
+      </x:c>
+      <x:c r="I12" s="68" t="str">
+        <x:v>电机整段运行超时</x:v>
+      </x:c>
+      <x:c r="J12" s="68" t="str">
+        <x:v>电机运行超时</x:v>
+      </x:c>
+      <x:c r="K12" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L12" s="73" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M12" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:50
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:72
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2028
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2352
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2355
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2362</x:v>
+      </x:c>
       <x:c r="N12" s="68" t="str">
-        <x:v>1-11 电机堵转</x:v>
+        <x:v>1-10 输入步进数错误</x:v>
       </x:c>
       <x:c r="O12" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P12"/>
     </x:row>
     <x:row r="13" ht="93" customHeight="1">
       <x:c r="A13" s="74" t="str">
-        <x:v>11-21</x:v>
+        <x:v>11-19</x:v>
       </x:c>
       <x:c r="B13" s="74" t="str">
-        <x:v>0x000B0015</x:v>
+        <x:v>0x000B0013</x:v>
       </x:c>
       <x:c r="C13" s="72" t="str">
         <x:v>MOTOR_PHASE_SHORT_ERROR</x:v>
@@ -1456,7 +1459,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E13" s="74" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F13" s="72" t="str">
         <x:v>电机驱动</x:v>
@@ -1489,16 +1492,16 @@
         <x:v>1-15 电机芯片报警</x:v>
       </x:c>
       <x:c r="O13" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P13"/>
     </x:row>
     <x:row r="14" ht="93" customHeight="1">
       <x:c r="A14" s="73" t="str">
-        <x:v>11-22</x:v>
+        <x:v>11-20</x:v>
       </x:c>
       <x:c r="B14" s="73" t="str">
-        <x:v>0x000B0016</x:v>
+        <x:v>0x000B0014</x:v>
       </x:c>
       <x:c r="C14" s="68" t="str">
         <x:v>MOTOR_PHASE_OPEN_ERROR</x:v>
@@ -1507,7 +1510,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E14" s="73" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="68" t="str">
         <x:v>电机驱动</x:v>
@@ -1540,16 +1543,16 @@
         <x:v>1-15 电机芯片报警</x:v>
       </x:c>
       <x:c r="O14" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P14"/>
     </x:row>
     <x:row r="15" ht="78" customHeight="1">
       <x:c r="A15" s="74" t="str">
-        <x:v>11-23</x:v>
+        <x:v>11-21</x:v>
       </x:c>
       <x:c r="B15" s="74" t="str">
-        <x:v>0x000B0017</x:v>
+        <x:v>0x000B0015</x:v>
       </x:c>
       <x:c r="C15" s="72" t="str">
         <x:v>MOTOR_DRIVER_OVERTEMP_WARNING</x:v>
@@ -1558,7 +1561,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E15" s="74" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="72" t="str">
         <x:v>电机驱动</x:v>
@@ -1590,16 +1593,16 @@
         <x:v>1-7 电机驱动器报警</x:v>
       </x:c>
       <x:c r="O15" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P15"/>
     </x:row>
     <x:row r="16" ht="94" customHeight="1">
       <x:c r="A16" s="73" t="str">
-        <x:v>11-24</x:v>
+        <x:v>11-22</x:v>
       </x:c>
       <x:c r="B16" s="73" t="str">
-        <x:v>0x000B0018</x:v>
+        <x:v>0x000B0016</x:v>
       </x:c>
       <x:c r="C16" s="68" t="str">
         <x:v>MOTOR_DRIVER_NOT_INITIALIZED</x:v>
@@ -1608,7 +1611,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E16" s="73" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="68" t="str">
         <x:v>电机驱动</x:v>
@@ -1643,16 +1646,16 @@
         <x:v>1-3 电机驱动异常重启；1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
       </x:c>
       <x:c r="O16" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P16"/>
     </x:row>
     <x:row r="17" ht="94" customHeight="1">
       <x:c r="A17" s="74" t="str">
-        <x:v>11-25</x:v>
+        <x:v>11-23</x:v>
       </x:c>
       <x:c r="B17" s="74" t="str">
-        <x:v>0x000B0019</x:v>
+        <x:v>0x000B0017</x:v>
       </x:c>
       <x:c r="C17" s="72" t="str">
         <x:v>MOTOR_STOP_WAIT_TIMEOUT</x:v>
@@ -1661,7 +1664,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E17" s="74" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F17" s="72" t="str">
         <x:v>电机驱动</x:v>
@@ -1696,16 +1699,16 @@
         <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
       </x:c>
       <x:c r="O17" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P17"/>
     </x:row>
     <x:row r="18" ht="94" customHeight="1">
       <x:c r="A18" s="73" t="str">
-        <x:v>11-26</x:v>
+        <x:v>11-24</x:v>
       </x:c>
       <x:c r="B18" s="73" t="str">
-        <x:v>0x000B001A</x:v>
+        <x:v>0x000B0018</x:v>
       </x:c>
       <x:c r="C18" s="68" t="str">
         <x:v>MOTOR_ARRIVAL_WAIT_TIMEOUT</x:v>
@@ -1714,7 +1717,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E18" s="73" t="n">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F18" s="68" t="str">
         <x:v>电机驱动</x:v>
@@ -1748,7 +1751,7 @@
         <x:v>1-10 输入步进数错误</x:v>
       </x:c>
       <x:c r="O18" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P18"/>
     </x:row>
@@ -1803,7 +1806,7 @@
         <x:v>2-1 与EC板通讯超时 （EC板和主控板通讯问题）</x:v>
       </x:c>
       <x:c r="O19" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P19"/>
     </x:row>
@@ -1851,7 +1854,7 @@
         <x:v>2-2 与EC板通讯编码数据校验错误</x:v>
       </x:c>
       <x:c r="O20" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P20"/>
     </x:row>
@@ -1902,7 +1905,7 @@
         <x:v>2-3 运行过程中丢步</x:v>
       </x:c>
       <x:c r="O21" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P21"/>
     </x:row>
@@ -1953,7 +1956,7 @@
         <x:v>2-5 读取断电编码值失败</x:v>
       </x:c>
       <x:c r="O22" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P22"/>
     </x:row>
@@ -2001,7 +2004,7 @@
         <x:v>2-6 上电后编码值变动；</x:v>
       </x:c>
       <x:c r="O23" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P23"/>
     </x:row>
@@ -2049,7 +2052,7 @@
         <x:v>2-10 固定点检测时编码值发生变化</x:v>
       </x:c>
       <x:c r="O24" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P24"/>
     </x:row>
@@ -2097,7 +2100,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O25" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P25"/>
     </x:row>
@@ -2145,7 +2148,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O26" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P26"/>
     </x:row>
@@ -2193,7 +2196,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O27" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P27"/>
     </x:row>
@@ -2241,7 +2244,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O28" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P28"/>
     </x:row>
@@ -2296,7 +2299,7 @@
         <x:v>2-1 与EC板通讯超时 （EC板和主控板通讯问题）</x:v>
       </x:c>
       <x:c r="O29" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P29"/>
     </x:row>
@@ -2351,7 +2354,7 @@
         <x:v>2-3 运行过程中丢步；2-10 固定点检测时编码值发生变化</x:v>
       </x:c>
       <x:c r="O30" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P30"/>
     </x:row>
@@ -2403,7 +2406,7 @@
         <x:v>3-1 传感器数据校验错误</x:v>
       </x:c>
       <x:c r="O31" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P31"/>
     </x:row>
@@ -2458,7 +2461,7 @@
         <x:v>3-2 密度传感器频率异常</x:v>
       </x:c>
       <x:c r="O32" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P32"/>
     </x:row>
@@ -2513,7 +2516,7 @@
         <x:v>3-3 密度传感器通信超时</x:v>
       </x:c>
       <x:c r="O33" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P33"/>
     </x:row>
@@ -2561,7 +2564,7 @@
         <x:v>3-5 二代密度传感器：密度传感器组件失效 三代密度传感器：与CPU0通讯超时</x:v>
       </x:c>
       <x:c r="O34" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P34"/>
     </x:row>
@@ -2610,7 +2613,7 @@
         <x:v>3-14 本次确认液体或者空气中角度值与上次差值大;</x:v>
       </x:c>
       <x:c r="O35" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P35"/>
     </x:row>
@@ -2658,7 +2661,7 @@
         <x:v>3-16 与密度管通讯校验错误</x:v>
       </x:c>
       <x:c r="O36" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P36"/>
     </x:row>
@@ -2706,7 +2709,7 @@
         <x:v>3-21 传感器扫频无谐振(FS) （探头频率&gt;17900或小于10010）</x:v>
       </x:c>
       <x:c r="O37" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P37"/>
     </x:row>
@@ -2757,7 +2760,7 @@
         <x:v>3-26 等同于3-12（3-26不会受密度分层影响） 1.二代密度传感器的频率异常 2.三代传感器的密度值异常； 3.温度无效值。</x:v>
       </x:c>
       <x:c r="O38" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P38"/>
     </x:row>
@@ -2812,7 +2815,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O39" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P39"/>
     </x:row>
@@ -2861,7 +2864,7 @@
         <x:v>3-3 密度传感器通信超时；3-5 二代密度传感器：密度传感器组件失效 三代密度传感器：与CPU0通讯超时</x:v>
       </x:c>
       <x:c r="O40" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P40"/>
     </x:row>
@@ -2909,7 +2912,7 @@
         <x:v>3-8 陀螺仪组件未响应；；3-10 读取陀螺仪时通信超时；</x:v>
       </x:c>
       <x:c r="O41" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P41"/>
     </x:row>
@@ -2958,7 +2961,7 @@
         <x:v>3-5 二代密度传感器：密度传感器组件失效 三代密度传感器：与CPU0通讯超时</x:v>
       </x:c>
       <x:c r="O42" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P42"/>
     </x:row>
@@ -3008,7 +3011,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O43" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P43"/>
     </x:row>
@@ -3058,7 +3061,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O44" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P44"/>
     </x:row>
@@ -3107,7 +3110,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O45" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P45"/>
     </x:row>
@@ -3156,7 +3159,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O46" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P46"/>
     </x:row>
@@ -3204,7 +3207,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O47" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P47"/>
     </x:row>
@@ -3254,7 +3257,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O48" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P48"/>
     </x:row>
@@ -3302,7 +3305,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O49" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P49"/>
     </x:row>
@@ -3355,7 +3358,7 @@
         <x:v>3-5 二代密度传感器：密度传感器组件失效 三代密度传感器：与CPU0通讯超时</x:v>
       </x:c>
       <x:c r="O50" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P50"/>
     </x:row>
@@ -3404,7 +3407,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O51" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P51"/>
     </x:row>
@@ -3455,7 +3458,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O52" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P52"/>
     </x:row>
@@ -3504,7 +3507,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O53" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P53"/>
     </x:row>
@@ -3552,7 +3555,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O54" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P54"/>
     </x:row>
@@ -3600,7 +3603,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O55" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P55"/>
     </x:row>
@@ -3650,7 +3653,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O56" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P56"/>
     </x:row>
@@ -3699,7 +3702,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O57" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P57"/>
     </x:row>
@@ -3748,7 +3751,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O58" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P58"/>
     </x:row>
@@ -3797,7 +3800,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O59" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P59"/>
     </x:row>
@@ -3846,7 +3849,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O60" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P60"/>
     </x:row>
@@ -3894,7 +3897,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O61" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P61"/>
     </x:row>
@@ -3942,7 +3945,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O62" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P62"/>
     </x:row>
@@ -3992,7 +3995,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O63" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P63"/>
     </x:row>
@@ -4040,7 +4043,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O64" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P64"/>
     </x:row>
@@ -4088,7 +4091,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O65" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P65"/>
     </x:row>
@@ -4136,7 +4139,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O66" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P66"/>
     </x:row>
@@ -4184,7 +4187,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O67" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P67"/>
     </x:row>
@@ -4232,7 +4235,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O68" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P68"/>
     </x:row>
@@ -4282,16 +4285,16 @@
         <x:v>4-9 越过零点位置XXmm报错（1.117以上版本）</x:v>
       </x:c>
       <x:c r="O69" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P69"/>
     </x:row>
     <x:row r="70" ht="78" customHeight="1">
       <x:c r="A70" s="73" t="str">
-        <x:v>14-12</x:v>
+        <x:v>14-11</x:v>
       </x:c>
       <x:c r="B70" s="73" t="str">
-        <x:v>0x000E000C</x:v>
+        <x:v>0x000E000B</x:v>
       </x:c>
       <x:c r="C70" s="68" t="str">
         <x:v>MEASUREMENT_ZERO_REPEAT_FAIL</x:v>
@@ -4300,7 +4303,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E70" s="73" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F70" s="68" t="str">
         <x:v>零点与位置检测</x:v>
@@ -4331,16 +4334,16 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O70" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P70"/>
     </x:row>
     <x:row r="71" ht="94" customHeight="1">
       <x:c r="A71" s="74" t="str">
-        <x:v>14-13</x:v>
+        <x:v>14-12</x:v>
       </x:c>
       <x:c r="B71" s="74" t="str">
-        <x:v>0x000E000D</x:v>
+        <x:v>0x000E000C</x:v>
       </x:c>
       <x:c r="C71" s="72" t="str">
         <x:v>POSITION_DATA_INVALID</x:v>
@@ -4349,7 +4352,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E71" s="74" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F71" s="72" t="str">
         <x:v>零点与位置检测</x:v>
@@ -4382,16 +4385,16 @@
         <x:v>2-10 固定点检测时编码值发生变化；4-9 越过零点位置XXmm报错（1.117以上版本）</x:v>
       </x:c>
       <x:c r="O71" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P71"/>
     </x:row>
     <x:row r="72" ht="63" customHeight="1">
       <x:c r="A72" s="73" t="str">
-        <x:v>14-14</x:v>
+        <x:v>14-13</x:v>
       </x:c>
       <x:c r="B72" s="73" t="str">
-        <x:v>0x000E000E</x:v>
+        <x:v>0x000E000D</x:v>
       </x:c>
       <x:c r="C72" s="68" t="str">
         <x:v>POSITION_TARGET_OVERRUN</x:v>
@@ -4400,7 +4403,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E72" s="73" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F72" s="68" t="str">
         <x:v>零点与位置检测</x:v>
@@ -4430,16 +4433,16 @@
         <x:v>4-9 越过零点位置XXmm报错（1.117以上版本）</x:v>
       </x:c>
       <x:c r="O72" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P72"/>
     </x:row>
     <x:row r="73" ht="78" customHeight="1">
       <x:c r="A73" s="74" t="str">
-        <x:v>14-15</x:v>
+        <x:v>14-14</x:v>
       </x:c>
       <x:c r="B73" s="74" t="str">
-        <x:v>0x000E000F</x:v>
+        <x:v>0x000E000E</x:v>
       </x:c>
       <x:c r="C73" s="72" t="str">
         <x:v>POSITION_ARRIVAL_DEVIATION</x:v>
@@ -4448,7 +4451,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E73" s="74" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F73" s="72" t="str">
         <x:v>零点与位置检测</x:v>
@@ -4479,16 +4482,16 @@
         <x:v>5-12 电机步进数和实际运行数差距大，拟合数据不正确；</x:v>
       </x:c>
       <x:c r="O73" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P73"/>
     </x:row>
     <x:row r="74" ht="94" customHeight="1">
       <x:c r="A74" s="73" t="str">
-        <x:v>14-16</x:v>
+        <x:v>14-15</x:v>
       </x:c>
       <x:c r="B74" s="73" t="str">
-        <x:v>0x000E0010</x:v>
+        <x:v>0x000E000F</x:v>
       </x:c>
       <x:c r="C74" s="68" t="str">
         <x:v>POSITION_MOTOR_NOT_STOPPED</x:v>
@@ -4497,7 +4500,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E74" s="73" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F74" s="68" t="str">
         <x:v>零点与位置检测</x:v>
@@ -4527,7 +4530,7 @@
         <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
       </x:c>
       <x:c r="O74" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P74"/>
     </x:row>
@@ -4576,7 +4579,7 @@
         <x:v>5-6 1.区间测量参数设置最高点高于罐高。 2.分布测量或每米测量液位高度高于罐高</x:v>
       </x:c>
       <x:c r="O75" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P75"/>
     </x:row>
@@ -4624,7 +4627,7 @@
         <x:v>5-15 液位变化超过最大跟随速度</x:v>
       </x:c>
       <x:c r="O76" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P76"/>
     </x:row>
@@ -4672,25 +4675,25 @@
         <x:v>5-16 罐高与标定时相差过大</x:v>
       </x:c>
       <x:c r="O77" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
       <x:c r="P77"/>
     </x:row>
     <x:row r="78" ht="94" customHeight="1">
       <x:c r="A78" s="73" t="str">
-        <x:v>15-18</x:v>
+        <x:v>15-17</x:v>
       </x:c>
       <x:c r="B78" s="73" t="str">
-        <x:v>0x000F0012</x:v>
+        <x:v>0x000F0011</x:v>
       </x:c>
       <x:c r="C78" s="68" t="str">
-        <x:v>MEASUREMENT_OILLEVEL_LOW</x:v>
+        <x:v>MEASUREMENT_DENSITY_LEVEL_TIMEOUT</x:v>
       </x:c>
       <x:c r="D78" s="73" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E78" s="73" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F78" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -4699,21 +4702,69 @@
         <x:v>测量流程</x:v>
       </x:c>
       <x:c r="H78" s="68" t="str">
-        <x:v>下行未找到液位</x:v>
+        <x:v>密度找液位超时</x:v>
       </x:c>
       <x:c r="I78" s="68" t="str">
-        <x:v>下行测量未找到液位</x:v>
+        <x:v>密度闭环找液位超时</x:v>
       </x:c>
       <x:c r="J78" s="68" t="str">
-        <x:v>下行未找到液位</x:v>
+        <x:v>密度找液位超时</x:v>
       </x:c>
       <x:c r="K78" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
       <x:c r="L78" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M78" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:597</x:v>
+      </x:c>
+      <x:c r="N78" s="68" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="O78" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+      <x:c r="P78"/>
+    </x:row>
+    <x:row r="79" ht="94" customHeight="1">
+      <x:c r="A79" s="74" t="str">
+        <x:v>15-18</x:v>
+      </x:c>
+      <x:c r="B79" s="74" t="str">
+        <x:v>0x000F0012</x:v>
+      </x:c>
+      <x:c r="C79" s="72" t="str">
+        <x:v>MEASUREMENT_OILLEVEL_LOW</x:v>
+      </x:c>
+      <x:c r="D79" s="74" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E79" s="74" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F79" s="72" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="G79" s="72" t="str">
+        <x:v>测量流程</x:v>
+      </x:c>
+      <x:c r="H79" s="72" t="str">
+        <x:v>下行未找到液位</x:v>
+      </x:c>
+      <x:c r="I79" s="72" t="str">
+        <x:v>下行测量未找到液位</x:v>
+      </x:c>
+      <x:c r="J79" s="72" t="str">
+        <x:v>下行未找到液位</x:v>
+      </x:c>
+      <x:c r="K79" s="74" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L79" s="74" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M78" s="68" t="str">
+      <x:c r="M79" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:954
 LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1471
 LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1497
@@ -4723,175 +4774,127 @@
 LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1949
 LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:375</x:v>
       </x:c>
-      <x:c r="N78" s="68" t="str">
+      <x:c r="N79" s="72" t="str">
         <x:v>6-4 油位太低；下行到盲区未检测到油。</x:v>
       </x:c>
-      <x:c r="O78" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-      <x:c r="P78"/>
-    </x:row>
-    <x:row r="79" ht="94" customHeight="1">
-      <x:c r="A79" s="74" t="str">
+      <x:c r="O79" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="93" customHeight="1">
+      <x:c r="A80" s="73" t="str">
         <x:v>15-19</x:v>
       </x:c>
-      <x:c r="B79" s="74" t="str">
+      <x:c r="B80" s="73" t="str">
         <x:v>0x000F0013</x:v>
       </x:c>
-      <x:c r="C79" s="72" t="str">
+      <x:c r="C80" s="68" t="str">
         <x:v>MEASUREMENT_OILLEVEL_NOTFOUND</x:v>
       </x:c>
-      <x:c r="D79" s="74" t="n">
+      <x:c r="D80" s="73" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E79" s="74" t="n">
+      <x:c r="E80" s="73" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F79" s="72" t="str">
+      <x:c r="F80" s="68" t="str">
         <x:v>测量过程</x:v>
       </x:c>
-      <x:c r="G79" s="72" t="str">
+      <x:c r="G80" s="68" t="str">
         <x:v>测量流程</x:v>
       </x:c>
-      <x:c r="H79" s="72" t="str">
+      <x:c r="H80" s="68" t="str">
         <x:v>上行未找到液位</x:v>
       </x:c>
-      <x:c r="I79" s="72" t="str">
+      <x:c r="I80" s="68" t="str">
         <x:v>上行测量未找到液位</x:v>
       </x:c>
-      <x:c r="J79" s="72" t="str">
+      <x:c r="J80" s="68" t="str">
         <x:v>上行未找到液位</x:v>
       </x:c>
-      <x:c r="K79" s="74" t="str">
+      <x:c r="K80" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
-      <x:c r="L79" s="74" t="n">
+      <x:c r="L80" s="73" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M79" s="72" t="str">
+      <x:c r="M80" s="68" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_density.c:963
 LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1154
 LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1201</x:v>
       </x:c>
-      <x:c r="N79" s="72" t="str">
+      <x:c r="N80" s="68" t="str">
         <x:v>6-5 运行到零点位置未找到液位；</x:v>
       </x:c>
-      <x:c r="O79" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="93" customHeight="1">
-      <x:c r="A80" s="73" t="str">
+      <x:c r="O80" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="78" customHeight="1">
+      <x:c r="A81" s="74" t="str">
         <x:v>15-20</x:v>
       </x:c>
-      <x:c r="B80" s="73" t="str">
+      <x:c r="B81" s="74" t="str">
         <x:v>0x000F0014</x:v>
       </x:c>
-      <x:c r="C80" s="68" t="str">
+      <x:c r="C81" s="72" t="str">
         <x:v>MEASUREMENT_WEIGHT_DOWN_FAIL</x:v>
       </x:c>
-      <x:c r="D80" s="73" t="n">
+      <x:c r="D81" s="74" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E80" s="73" t="n">
+      <x:c r="E81" s="74" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F80" s="68" t="str">
+      <x:c r="F81" s="72" t="str">
         <x:v>测量过程</x:v>
       </x:c>
-      <x:c r="G80" s="68" t="str">
+      <x:c r="G81" s="72" t="str">
         <x:v>测量流程</x:v>
       </x:c>
-      <x:c r="H80" s="68" t="str">
+      <x:c r="H81" s="72" t="str">
         <x:v>下行寻重失败</x:v>
       </x:c>
-      <x:c r="I80" s="68" t="str">
+      <x:c r="I81" s="72" t="str">
         <x:v>下行寻重失败</x:v>
       </x:c>
-      <x:c r="J80" s="68" t="str">
+      <x:c r="J81" s="72" t="str">
         <x:v>下行寻重失败</x:v>
       </x:c>
-      <x:c r="K80" s="73" t="str">
+      <x:c r="K81" s="74" t="str">
         <x:v>使用中</x:v>
       </x:c>
-      <x:c r="L80" s="73" t="n">
+      <x:c r="L81" s="74" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M80" s="68" t="str">
+      <x:c r="M81" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1354
 LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:85
 LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:544
 LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:642</x:v>
       </x:c>
-      <x:c r="N80" s="68" t="str">
+      <x:c r="N81" s="72" t="str">
         <x:v>4-4 测量罐底，下行到达罐高+最大下行位置；</x:v>
       </x:c>
-      <x:c r="O80" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="78" customHeight="1">
-      <x:c r="A81" s="74" t="str">
-        <x:v>15-21</x:v>
-      </x:c>
-      <x:c r="B81" s="74" t="str">
-        <x:v>0x000F0015</x:v>
-      </x:c>
-      <x:c r="C81" s="72" t="str">
-        <x:v>MEASUREMENT_WEIGHT_UP_FAIL</x:v>
-      </x:c>
-      <x:c r="D81" s="74" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E81" s="74" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F81" s="72" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="G81" s="72" t="str">
-        <x:v>测量流程</x:v>
-      </x:c>
-      <x:c r="H81" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
-      </x:c>
-      <x:c r="I81" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
-      </x:c>
-      <x:c r="J81" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
-      </x:c>
-      <x:c r="K81" s="74" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L81" s="74" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M81" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_zero.c:338</x:v>
-      </x:c>
-      <x:c r="N81" s="72" t="str">
-        <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
-      </x:c>
       <x:c r="O81" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="78" customHeight="1">
       <x:c r="A82" s="73" t="str">
-        <x:v>15-22</x:v>
+        <x:v>15-21</x:v>
       </x:c>
       <x:c r="B82" s="73" t="str">
-        <x:v>0x000F0016</x:v>
+        <x:v>0x000F0015</x:v>
       </x:c>
       <x:c r="C82" s="68" t="str">
-        <x:v>MEASUREMENT_WATERLEVEL_LOW</x:v>
+        <x:v>MEASUREMENT_WEIGHT_UP_FAIL</x:v>
       </x:c>
       <x:c r="D82" s="73" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E82" s="73" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F82" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -4900,21 +4903,68 @@
         <x:v>测量流程</x:v>
       </x:c>
       <x:c r="H82" s="68" t="str">
-        <x:v>下行未找到水位</x:v>
+        <x:v>上行寻重失败</x:v>
       </x:c>
       <x:c r="I82" s="68" t="str">
-        <x:v>下行测量未找到水位</x:v>
+        <x:v>上行寻重失败</x:v>
       </x:c>
       <x:c r="J82" s="68" t="str">
-        <x:v>下行未找到水位</x:v>
+        <x:v>上行寻重失败</x:v>
       </x:c>
       <x:c r="K82" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
       <x:c r="L82" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M82" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_zero.c:338</x:v>
+      </x:c>
+      <x:c r="N82" s="68" t="str">
+        <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
+      </x:c>
+      <x:c r="O82" s="68" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="78" customHeight="1">
+      <x:c r="A83" s="74" t="str">
+        <x:v>15-22</x:v>
+      </x:c>
+      <x:c r="B83" s="74" t="str">
+        <x:v>0x000F0016</x:v>
+      </x:c>
+      <x:c r="C83" s="72" t="str">
+        <x:v>MEASUREMENT_WATERLEVEL_LOW</x:v>
+      </x:c>
+      <x:c r="D83" s="74" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E83" s="74" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F83" s="72" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="G83" s="72" t="str">
+        <x:v>测量流程</x:v>
+      </x:c>
+      <x:c r="H83" s="72" t="str">
+        <x:v>下行未找到水位</x:v>
+      </x:c>
+      <x:c r="I83" s="72" t="str">
+        <x:v>下行测量未找到水位</x:v>
+      </x:c>
+      <x:c r="J83" s="72" t="str">
+        <x:v>下行未找到水位</x:v>
+      </x:c>
+      <x:c r="K83" s="74" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="L83" s="74" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="M82" s="68" t="str">
+      <x:c r="M83" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:273
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:333
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:578
@@ -4922,126 +4972,79 @@
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:660
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:863</x:v>
       </x:c>
-      <x:c r="N82" s="68" t="str">
+      <x:c r="N83" s="72" t="str">
         <x:v>6-3 1.找水位时上行到了零点；</x:v>
       </x:c>
-      <x:c r="O82" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="78" customHeight="1">
-      <x:c r="A83" s="74" t="str">
+      <x:c r="O83" s="72" t="str">
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="78" customHeight="1">
+      <x:c r="A84" s="73" t="str">
         <x:v>15-23</x:v>
       </x:c>
-      <x:c r="B83" s="74" t="str">
+      <x:c r="B84" s="73" t="str">
         <x:v>0x000F0017</x:v>
       </x:c>
-      <x:c r="C83" s="72" t="str">
+      <x:c r="C84" s="68" t="str">
         <x:v>MEASUREMENT_DENSITY_NO_VALID_POINT</x:v>
       </x:c>
-      <x:c r="D83" s="74" t="n">
+      <x:c r="D84" s="73" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E83" s="74" t="n">
+      <x:c r="E84" s="73" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F83" s="72" t="str">
+      <x:c r="F84" s="68" t="str">
         <x:v>测量过程</x:v>
       </x:c>
-      <x:c r="G83" s="72" t="str">
+      <x:c r="G84" s="68" t="str">
         <x:v>测量流程</x:v>
       </x:c>
-      <x:c r="H83" s="72" t="str">
+      <x:c r="H84" s="68" t="str">
         <x:v>密度测量无有效点</x:v>
       </x:c>
-      <x:c r="I83" s="72" t="str">
+      <x:c r="I84" s="68" t="str">
         <x:v>密度分布测量无有效测点</x:v>
       </x:c>
-      <x:c r="J83" s="72" t="str">
+      <x:c r="J84" s="68" t="str">
         <x:v>密度测量无有效点</x:v>
       </x:c>
-      <x:c r="K83" s="74" t="str">
+      <x:c r="K84" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
-      <x:c r="L83" s="74" t="n">
+      <x:c r="L84" s="73" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="M83" s="72" t="str">
+      <x:c r="M84" s="68" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_density.c:352
 LTD_MAIN_CPU2/Application/Src/measure_density.c:959
 LTD_MAIN_CPU2/Application/Src/measure_density.c:1490
 LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:456
 LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:586</x:v>
       </x:c>
-      <x:c r="N83" s="72" t="str">
-        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
-      </x:c>
-      <x:c r="O83" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="78" customHeight="1">
-      <x:c r="A84" s="73" t="str">
-        <x:v>15-24</x:v>
-      </x:c>
-      <x:c r="B84" s="73" t="str">
-        <x:v>0x000F0018</x:v>
-      </x:c>
-      <x:c r="C84" s="68" t="str">
-        <x:v>MEASUREMENT_DENSITY_SURFACE_NOTFOUND</x:v>
-      </x:c>
-      <x:c r="D84" s="73" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E84" s="73" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F84" s="68" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="G84" s="68" t="str">
-        <x:v>测量流程</x:v>
-      </x:c>
-      <x:c r="H84" s="68" t="str">
-        <x:v>密度测量未找到油面</x:v>
-      </x:c>
-      <x:c r="I84" s="68" t="str">
-        <x:v>密度分布测量未找到油面</x:v>
-      </x:c>
-      <x:c r="J84" s="68" t="str">
-        <x:v>密度测量未找到油面</x:v>
-      </x:c>
-      <x:c r="K84" s="73" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="L84" s="73" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M84" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:581</x:v>
-      </x:c>
       <x:c r="N84" s="68" t="str">
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O84" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="94" customHeight="1">
       <x:c r="A85" s="74" t="str">
-        <x:v>15-25</x:v>
+        <x:v>15-24</x:v>
       </x:c>
       <x:c r="B85" s="74" t="str">
-        <x:v>0x000F0019</x:v>
+        <x:v>0x000F0018</x:v>
       </x:c>
       <x:c r="C85" s="72" t="str">
-        <x:v>MEASUREMENT_DENSITY_LEVEL_TIMEOUT</x:v>
+        <x:v>MEASUREMENT_DENSITY_SURFACE_NOTFOUND</x:v>
       </x:c>
       <x:c r="D85" s="74" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E85" s="74" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F85" s="72" t="str">
         <x:v>测量过程</x:v>
@@ -5050,13 +5053,13 @@
         <x:v>测量流程</x:v>
       </x:c>
       <x:c r="H85" s="72" t="str">
-        <x:v>密度找液位超时</x:v>
+        <x:v>密度测量未找到油面</x:v>
       </x:c>
       <x:c r="I85" s="72" t="str">
-        <x:v>密度闭环找液位超时</x:v>
+        <x:v>密度分布测量未找到油面</x:v>
       </x:c>
       <x:c r="J85" s="72" t="str">
-        <x:v>密度找液位超时</x:v>
+        <x:v>密度测量未找到油面</x:v>
       </x:c>
       <x:c r="K85" s="74" t="str">
         <x:v>使用中</x:v>
@@ -5065,21 +5068,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M85" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:597</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:581</x:v>
       </x:c>
       <x:c r="N85" s="72" t="str">
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O85" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="94" customHeight="1">
       <x:c r="A86" s="73" t="str">
-        <x:v>15-26</x:v>
+        <x:v>15-25</x:v>
       </x:c>
       <x:c r="B86" s="73" t="str">
-        <x:v>0x000F001A</x:v>
+        <x:v>0x000F0019</x:v>
       </x:c>
       <x:c r="C86" s="68" t="str">
         <x:v>MEASUREMENT_FREQUENCY_LEVEL_TIMEOUT</x:v>
@@ -5088,7 +5091,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E86" s="73" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F86" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -5118,15 +5121,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O86" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="94" customHeight="1">
       <x:c r="A87" s="74" t="str">
-        <x:v>15-27</x:v>
+        <x:v>15-26</x:v>
       </x:c>
       <x:c r="B87" s="74" t="str">
-        <x:v>0x000F001B</x:v>
+        <x:v>0x000F001A</x:v>
       </x:c>
       <x:c r="C87" s="72" t="str">
         <x:v>MEASUREMENT_BOTTOM_RELEASE_FAIL</x:v>
@@ -5135,7 +5138,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E87" s="74" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F87" s="72" t="str">
         <x:v>测量过程</x:v>
@@ -5165,15 +5168,15 @@
         <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
       </x:c>
       <x:c r="O87" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="94" customHeight="1">
       <x:c r="A88" s="73" t="str">
-        <x:v>15-28</x:v>
+        <x:v>15-27</x:v>
       </x:c>
       <x:c r="B88" s="73" t="str">
-        <x:v>0x000F001C</x:v>
+        <x:v>0x000F001B</x:v>
       </x:c>
       <x:c r="C88" s="68" t="str">
         <x:v>MEASUREMENT_TANK_HEIGHT_NOT_CONFIGURED</x:v>
@@ -5182,7 +5185,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E88" s="73" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F88" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -5213,15 +5216,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O88" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="94" customHeight="1">
       <x:c r="A89" s="74" t="str">
-        <x:v>15-29</x:v>
+        <x:v>15-28</x:v>
       </x:c>
       <x:c r="B89" s="74" t="str">
-        <x:v>0x000F001D</x:v>
+        <x:v>0x000F001C</x:v>
       </x:c>
       <x:c r="C89" s="72" t="str">
         <x:v>MEASUREMENT_WATER_CALIBRATION_NOT_CONFIGURED</x:v>
@@ -5230,7 +5233,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E89" s="74" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F89" s="72" t="str">
         <x:v>测量过程</x:v>
@@ -5261,15 +5264,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O89" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
       <x:c r="A90" s="73" t="str">
-        <x:v>15-31</x:v>
+        <x:v>15-29</x:v>
       </x:c>
       <x:c r="B90" s="73" t="str">
-        <x:v>0x000F001F</x:v>
+        <x:v>0x000F001D</x:v>
       </x:c>
       <x:c r="C90" s="68" t="str">
         <x:v>MEASUREMENT_DENSITY_PLAN_INVALID</x:v>
@@ -5278,7 +5281,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E90" s="73" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F90" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -5315,15 +5318,15 @@
         <x:v>5-4 1.进行单点监测或单点测量时，输入的检测位置小于盲区位置或高于罐高。 2.区间测量输入液位区间错误；5-5 密度分布测量或标定液位时，液位值过低； 2.区间测量参数设置最低点要＞（盲区+300）；否侧报错；5-6 1.区间测量参数设置最高点高于罐高。 2.分布测量或每米测量液位高度高于罐高；5-7 密度分布测量点数超过100（加测点过多）</x:v>
       </x:c>
       <x:c r="O90" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
       <x:c r="A91" s="74" t="str">
-        <x:v>15-32</x:v>
+        <x:v>15-30</x:v>
       </x:c>
       <x:c r="B91" s="74" t="str">
-        <x:v>0x000F0020</x:v>
+        <x:v>0x000F001E</x:v>
       </x:c>
       <x:c r="C91" s="72" t="str">
         <x:v>MEASUREMENT_TANK_HEIGHT_RESULT_INVALID</x:v>
@@ -5332,7 +5335,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E91" s="74" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F91" s="72" t="str">
         <x:v>测量过程</x:v>
@@ -5363,15 +5366,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O91" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="78" customHeight="1">
       <x:c r="A92" s="73" t="str">
-        <x:v>15-33</x:v>
+        <x:v>15-31</x:v>
       </x:c>
       <x:c r="B92" s="73" t="str">
-        <x:v>0x000F0021</x:v>
+        <x:v>0x000F001F</x:v>
       </x:c>
       <x:c r="C92" s="68" t="str">
         <x:v>MEASUREMENT_WATER_CALC_OUT_OF_RANGE</x:v>
@@ -5380,7 +5383,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E92" s="73" t="n">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F92" s="68" t="str">
         <x:v>测量过程</x:v>
@@ -5411,7 +5414,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O92" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="78" customHeight="1">
@@ -5459,7 +5462,7 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="O93" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="94" customHeight="1">
@@ -5508,7 +5511,7 @@
         <x:v>7-2 没有存储置零点时的角度值。</x:v>
       </x:c>
       <x:c r="O94" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
@@ -5562,7 +5565,7 @@
         <x:v>5-4 1.进行单点监测或单点测量时，输入的检测位置小于盲区位置或高于罐高。 2.区间测量输入液位区间错误；5-5 密度分布测量或标定液位时，液位值过低； 2.区间测量参数设置最低点要＞（盲区+300）；否侧报错；5-6 1.区间测量参数设置最高点高于罐高。 2.分布测量或每米测量液位高度高于罐高；5-7 密度分布测量点数超过100（加测点过多）</x:v>
       </x:c>
       <x:c r="O95" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
@@ -5609,7 +5612,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O96" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="63" customHeight="1">
@@ -5663,7 +5666,7 @@
         <x:v>7-1 主控板中存储器的参数异常；；7-2 没有存储置零点时的角度值。</x:v>
       </x:c>
       <x:c r="O97" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="48" customHeight="1">
@@ -5713,7 +5716,7 @@
         <x:v>5-4 1.进行单点监测或单点测量时，输入的检测位置小于盲区位置或高于罐高。 2.区间测量输入液位区间错误；5-5 密度分布测量或标定液位时，液位值过低； 2.区间测量参数设置最低点要＞（盲区+300）；否侧报错；5-6 1.区间测量参数设置最高点高于罐高。 2.分布测量或每米测量液位高度高于罐高；5-7 密度分布测量点数超过100（加测点过多）</x:v>
       </x:c>
       <x:c r="O98" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="48" customHeight="1">
@@ -5764,7 +5767,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O99" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="34" customHeight="1">
@@ -5812,7 +5815,7 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="O100" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="34" customHeight="1">
@@ -5860,7 +5863,7 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="O101" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="94" customHeight="1">
@@ -5911,7 +5914,7 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="O102" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="34" customHeight="1">
@@ -5965,7 +5968,7 @@
         <x:v>8-2 AD5421写控制寄存器失败；8-3 上电自检_电流芯片报警</x:v>
       </x:c>
       <x:c r="O103" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="34" customHeight="1">
@@ -6015,15 +6018,15 @@
         <x:v>8-6 输入电流对比异常</x:v>
       </x:c>
       <x:c r="O104" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="63" customHeight="1">
       <x:c r="A105" s="74" t="str">
-        <x:v>18-10</x:v>
+        <x:v>18-9</x:v>
       </x:c>
       <x:c r="B105" s="74" t="str">
-        <x:v>0x0012000A</x:v>
+        <x:v>0x00120009</x:v>
       </x:c>
       <x:c r="C105" s="72" t="str">
         <x:v>AD5421_INTERNAL_COMM_ERROR</x:v>
@@ -6032,7 +6035,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E105" s="74" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F105" s="72" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6064,15 +6067,15 @@
         <x:v>8-3 上电自检_电流芯片报警</x:v>
       </x:c>
       <x:c r="O105" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="94" customHeight="1">
       <x:c r="A106" s="73" t="str">
-        <x:v>18-11</x:v>
+        <x:v>18-10</x:v>
       </x:c>
       <x:c r="B106" s="73" t="str">
-        <x:v>0x0012000B</x:v>
+        <x:v>0x0012000A</x:v>
       </x:c>
       <x:c r="C106" s="68" t="str">
         <x:v>AD5421_LOOP_CURRENT_HIGH</x:v>
@@ -6081,7 +6084,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E106" s="73" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="68" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6113,15 +6116,15 @@
         <x:v>8-3 上电自检_电流芯片报警；8-6 输入电流对比异常</x:v>
       </x:c>
       <x:c r="O106" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="94" customHeight="1">
       <x:c r="A107" s="74" t="str">
-        <x:v>18-12</x:v>
+        <x:v>18-11</x:v>
       </x:c>
       <x:c r="B107" s="74" t="str">
-        <x:v>0x0012000C</x:v>
+        <x:v>0x0012000B</x:v>
       </x:c>
       <x:c r="C107" s="72" t="str">
         <x:v>AD5421_LOOP_CURRENT_LOW</x:v>
@@ -6130,7 +6133,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E107" s="74" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F107" s="72" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6162,15 +6165,15 @@
         <x:v>8-3 上电自检_电流芯片报警；8-6 输入电流对比异常</x:v>
       </x:c>
       <x:c r="O107" s="72" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="63" customHeight="1">
       <x:c r="A108" s="73" t="str">
-        <x:v>18-13</x:v>
+        <x:v>18-12</x:v>
       </x:c>
       <x:c r="B108" s="73" t="str">
-        <x:v>0x0012000D</x:v>
+        <x:v>0x0012000C</x:v>
       </x:c>
       <x:c r="C108" s="68" t="str">
         <x:v>AD5421_LOOP_VOLTAGE_LOW</x:v>
@@ -6179,7 +6182,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E108" s="73" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F108" s="68" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6211,15 +6214,15 @@
         <x:v>8-4 设备供电电压异常</x:v>
       </x:c>
       <x:c r="O108" s="68" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="57" customHeight="1">
       <x:c r="A109" s="99" t="str">
-        <x:v>18-14</x:v>
+        <x:v>18-13</x:v>
       </x:c>
       <x:c r="B109" s="99" t="str">
-        <x:v>0x0012000E</x:v>
+        <x:v>0x0012000D</x:v>
       </x:c>
       <x:c r="C109" s="99" t="str">
         <x:v>AD5421_SPI_TRANSFER_ERROR</x:v>
@@ -6228,7 +6231,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E109" s="99" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F109" s="99" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6265,15 +6268,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O109" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="57" customHeight="1">
       <x:c r="A110" s="99" t="str">
-        <x:v>18-15</x:v>
+        <x:v>18-14</x:v>
       </x:c>
       <x:c r="B110" s="99" t="str">
-        <x:v>0x0012000F</x:v>
+        <x:v>0x0012000E</x:v>
       </x:c>
       <x:c r="C110" s="99" t="str">
         <x:v>AD5421_ACCESS_BUSY</x:v>
@@ -6282,7 +6285,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E110" s="99" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F110" s="99" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6318,15 +6321,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O110" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="57" customHeight="1">
       <x:c r="A111" s="99" t="str">
-        <x:v>18-16</x:v>
+        <x:v>18-15</x:v>
       </x:c>
       <x:c r="B111" s="99" t="str">
-        <x:v>0x00120010</x:v>
+        <x:v>0x0012000F</x:v>
       </x:c>
       <x:c r="C111" s="99" t="str">
         <x:v>AD5421_OVERTEMP_SHUTDOWN</x:v>
@@ -6335,7 +6338,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E111" s="99" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F111" s="99" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6369,15 +6372,15 @@
         <x:v>8-8 芯片温度过高</x:v>
       </x:c>
       <x:c r="O111" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="57" customHeight="1">
       <x:c r="A112" s="99" t="str">
-        <x:v>18-17</x:v>
+        <x:v>18-16</x:v>
       </x:c>
       <x:c r="B112" s="99" t="str">
-        <x:v>0x00120011</x:v>
+        <x:v>0x00120010</x:v>
       </x:c>
       <x:c r="C112" s="99" t="str">
         <x:v>AD5421_OVERTEMP_WARNING</x:v>
@@ -6386,7 +6389,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E112" s="99" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F112" s="99" t="str">
         <x:v>模拟输出与自检</x:v>
@@ -6420,7 +6423,7 @@
         <x:v>8-8 芯片温度过高</x:v>
       </x:c>
       <x:c r="O112" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="57" customHeight="1">
@@ -6474,7 +6477,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O113" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="57" customHeight="1">
@@ -6521,7 +6524,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O114" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="57" customHeight="1">
@@ -6568,7 +6571,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O115" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="57" customHeight="1">
@@ -6617,7 +6620,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O116" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="57" customHeight="1">
@@ -6666,7 +6669,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O117" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="57" customHeight="1">
@@ -6720,7 +6723,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O118" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="57" customHeight="1">
@@ -6767,7 +6770,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O119" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="57" customHeight="1">
@@ -6814,7 +6817,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O120" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="57" customHeight="1">
@@ -6862,7 +6865,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O121" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="57" customHeight="1">
@@ -6909,7 +6912,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O122" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="57" customHeight="1">
@@ -6956,7 +6959,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O123" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="57" customHeight="1">
@@ -7003,7 +7006,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O124" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="57" customHeight="1">
@@ -7050,7 +7053,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O125" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="57" customHeight="1">
@@ -7104,7 +7107,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O126" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="57" customHeight="1">
@@ -7151,7 +7154,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O127" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="57" customHeight="1">
@@ -7198,7 +7201,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O128" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="57" customHeight="1">
@@ -7247,15 +7250,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O129" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="57" customHeight="1">
       <x:c r="A130" s="99" t="str">
-        <x:v>22-4</x:v>
+        <x:v>22-1</x:v>
       </x:c>
       <x:c r="B130" s="99" t="str">
-        <x:v>0x00160004</x:v>
+        <x:v>0x00160001</x:v>
       </x:c>
       <x:c r="C130" s="99" t="str">
         <x:v>SYSTEM_BUFFER_CAPACITY_ERROR</x:v>
@@ -7264,7 +7267,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E130" s="99" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F130" s="99" t="str">
         <x:v>系统与软件</x:v>
@@ -7297,15 +7300,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O130" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="57" customHeight="1">
       <x:c r="A131" s="99" t="str">
-        <x:v>22-5</x:v>
+        <x:v>22-2</x:v>
       </x:c>
       <x:c r="B131" s="99" t="str">
-        <x:v>0x00160005</x:v>
+        <x:v>0x00160002</x:v>
       </x:c>
       <x:c r="C131" s="99" t="str">
         <x:v>SYSTEM_CALL_CONDITION_ERROR</x:v>
@@ -7314,7 +7317,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E131" s="99" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F131" s="99" t="str">
         <x:v>系统与软件</x:v>
@@ -7351,15 +7354,15 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O131" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="57" customHeight="1">
       <x:c r="A132" s="99" t="str">
-        <x:v>22-6</x:v>
+        <x:v>22-3</x:v>
       </x:c>
       <x:c r="B132" s="99" t="str">
-        <x:v>0x00160006</x:v>
+        <x:v>0x00160003</x:v>
       </x:c>
       <x:c r="C132" s="99" t="str">
         <x:v>SYSTEM_CALCULATION_ERROR</x:v>
@@ -7368,7 +7371,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E132" s="99" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F132" s="99" t="str">
         <x:v>系统与软件</x:v>
@@ -7399,7 +7402,7 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="O132" s="99" t="str">
-        <x:v>当前开发版；正式发布后按首个适用CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>协议23正式版；CPU2 V1.28.0.0 / CPU3 V1.26.0.0；旧版按对应历史页解释</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7533,29 +7536,31 @@
     </x:row>
     <x:row r="3" ht="108" customHeight="1">
       <x:c r="A3" s="74" t="str">
-        <x:v>11-4</x:v>
+        <x:v>11-3</x:v>
       </x:c>
       <x:c r="B3" s="72" t="str">
-        <x:v>MOTOR_DISABLED</x:v>
+        <x:v>MOTOR_TMC_CONFIG_LOST</x:v>
       </x:c>
       <x:c r="C3" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:48
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:70
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1071
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1075
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_driver_param.c:162</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_manager.c:68
+LTD_MAIN_CPU2/Application/Src/fault_recovery.c:46
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:68
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:881
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:888
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1021
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1028</x:v>
       </x:c>
       <x:c r="D3" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E3" s="72" t="str">
-        <x:v>电机驱动未使能</x:v>
+        <x:v>电机驱动配置丢失</x:v>
       </x:c>
       <x:c r="F3" s="72" t="str">
-        <x:v>电机驱动输出未使能</x:v>
+        <x:v>TMC5130运行期复位或关键配置丢失</x:v>
       </x:c>
       <x:c r="G3" s="72" t="str">
-        <x:v>电机驱动未使能</x:v>
+        <x:v>电机驱动配置丢失</x:v>
       </x:c>
       <x:c r="H3" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7567,7 +7572,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K3" s="72" t="str">
-        <x:v>1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
+        <x:v>1-3 电机驱动异常重启</x:v>
       </x:c>
       <x:c r="L3"/>
       <x:c r="M3"/>
@@ -7582,26 +7587,29 @@
     </x:row>
     <x:row r="4" ht="63" customHeight="1">
       <x:c r="A4" s="73" t="str">
-        <x:v>11-5</x:v>
+        <x:v>11-4</x:v>
       </x:c>
       <x:c r="B4" s="68" t="str">
-        <x:v>MOTOR_UNKNOWN_FEEDBACK</x:v>
+        <x:v>MOTOR_DISABLED</x:v>
       </x:c>
       <x:c r="C4" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:70
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:964</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:48
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:70
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1071
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1075
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_driver_param.c:162</x:v>
       </x:c>
       <x:c r="D4" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E4" s="68" t="str">
-        <x:v>电机反馈未知</x:v>
+        <x:v>电机驱动未使能</x:v>
       </x:c>
       <x:c r="F4" s="68" t="str">
-        <x:v>电机反馈状态无法识别</x:v>
+        <x:v>电机驱动输出未使能</x:v>
       </x:c>
       <x:c r="G4" s="68" t="str">
-        <x:v>电机反馈未知</x:v>
+        <x:v>电机驱动未使能</x:v>
       </x:c>
       <x:c r="H4" s="68" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7613,7 +7621,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K4" s="68" t="str">
-        <x:v>1-5 电机状态异常</x:v>
+        <x:v>1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4"/>
@@ -7628,28 +7636,26 @@
     </x:row>
     <x:row r="5" ht="108" customHeight="1">
       <x:c r="A5" s="74" t="str">
-        <x:v>11-10</x:v>
+        <x:v>11-5</x:v>
       </x:c>
       <x:c r="B5" s="72" t="str">
-        <x:v>MOTOR_STEP_ERROR</x:v>
+        <x:v>MOTOR_UNKNOWN_FEEDBACK</x:v>
       </x:c>
       <x:c r="C5" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1108
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1111
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1122
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2024</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:70
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:964</x:v>
       </x:c>
       <x:c r="D5" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E5" s="72" t="str">
-        <x:v>电机无有效位移</x:v>
+        <x:v>电机反馈未知</x:v>
       </x:c>
       <x:c r="F5" s="72" t="str">
-        <x:v>丢步检测</x:v>
+        <x:v>电机反馈状态无法识别</x:v>
       </x:c>
       <x:c r="G5" s="72" t="str">
-        <x:v>电机无有效位移</x:v>
+        <x:v>电机反馈未知</x:v>
       </x:c>
       <x:c r="H5" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7661,7 +7667,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K5" s="72" t="str">
-        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
+        <x:v>1-5 电机状态异常</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5"/>
@@ -7676,27 +7682,28 @@
     </x:row>
     <x:row r="6" ht="78" customHeight="1">
       <x:c r="A6" s="73" t="str">
-        <x:v>11-16</x:v>
+        <x:v>11-10</x:v>
       </x:c>
       <x:c r="B6" s="68" t="str">
-        <x:v>MOTOR_CHARGE_PUMP_UNDER_VOLTAGE</x:v>
+        <x:v>MOTOR_STEP_ERROR</x:v>
       </x:c>
       <x:c r="C6" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:47
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:69
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:998</x:v>
+        <x:v>LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1108
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1111
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:1122
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2024</x:v>
       </x:c>
       <x:c r="D6" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E6" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
+        <x:v>电机无有效位移</x:v>
       </x:c>
       <x:c r="F6" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
+        <x:v>丢步检测</x:v>
       </x:c>
       <x:c r="G6" s="68" t="str">
-        <x:v>电荷泵欠压</x:v>
+        <x:v>电机无有效位移</x:v>
       </x:c>
       <x:c r="H6" s="68" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7708,7 +7715,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K6" s="68" t="str">
-        <x:v>1-7 电机驱动器报警</x:v>
+        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6"/>
@@ -7723,27 +7730,27 @@
     </x:row>
     <x:row r="7" ht="78" customHeight="1">
       <x:c r="A7" s="74" t="str">
-        <x:v>11-17</x:v>
+        <x:v>11-11</x:v>
       </x:c>
       <x:c r="B7" s="72" t="str">
-        <x:v>MOTOR_OVERTEMPERATURE</x:v>
+        <x:v>MOTOR_STALL_ERROR</x:v>
       </x:c>
       <x:c r="C7" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:71
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:101
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:142</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:72
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:97
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:148</x:v>
       </x:c>
       <x:c r="D7" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E7" s="72" t="str">
-        <x:v>电机驱动过温关断</x:v>
+        <x:v>电机堵转</x:v>
       </x:c>
       <x:c r="F7" s="72" t="str">
-        <x:v>电机驱动已过温关断</x:v>
+        <x:v>电机堵转或负载阻力过大</x:v>
       </x:c>
       <x:c r="G7" s="72" t="str">
-        <x:v>电机驱动过温停止</x:v>
+        <x:v>电机运行阻力大</x:v>
       </x:c>
       <x:c r="H7" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7755,7 +7762,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K7" s="72" t="str">
-        <x:v>1-7 电机驱动器报警</x:v>
+        <x:v>1-11 电机堵转</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7"/>
@@ -7770,42 +7777,39 @@
     </x:row>
     <x:row r="8" ht="110" customHeight="1">
       <x:c r="A8" s="73" t="str">
-        <x:v>11-18</x:v>
+        <x:v>11-16</x:v>
       </x:c>
       <x:c r="B8" s="68" t="str">
-        <x:v>MOTOR_RUN_TIMEOUT</x:v>
+        <x:v>MOTOR_CHARGE_PUMP_UNDER_VOLTAGE</x:v>
       </x:c>
       <x:c r="C8" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:50
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:72
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2028
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2352
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2355
-LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2362</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:47
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:69
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:998</x:v>
       </x:c>
       <x:c r="D8" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E8" s="68" t="str">
-        <x:v>电机运行超时</x:v>
+        <x:v>电荷泵欠压</x:v>
       </x:c>
       <x:c r="F8" s="68" t="str">
-        <x:v>电机整段运行超时</x:v>
+        <x:v>电荷泵欠压</x:v>
       </x:c>
       <x:c r="G8" s="68" t="str">
-        <x:v>电机运行超时</x:v>
+        <x:v>电荷泵欠压</x:v>
       </x:c>
       <x:c r="H8" s="68" t="str">
-        <x:v>可在部件状态恢复后按命令白名单重跑</x:v>
+        <x:v>按现有命令白名单和故障恢复边界处理</x:v>
       </x:c>
       <x:c r="I8" s="68" t="str">
         <x:v>来源、名称、原因和CPU3显示均已覆盖</x:v>
       </x:c>
       <x:c r="J8" s="68" t="str">
-        <x:v>故障注入11-18，核对屏幕编号、日志原因、停机和恢复口径</x:v>
+        <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K8" s="68" t="str">
-        <x:v>1-10 输入步进数错误</x:v>
+        <x:v>1-7 电机驱动器报警</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8"/>
@@ -7820,31 +7824,27 @@
     </x:row>
     <x:row r="9" ht="110" customHeight="1">
       <x:c r="A9" s="74" t="str">
-        <x:v>11-19</x:v>
+        <x:v>11-17</x:v>
       </x:c>
       <x:c r="B9" s="72" t="str">
-        <x:v>MOTOR_TMC_CONFIG_LOST</x:v>
+        <x:v>MOTOR_OVERTEMPERATURE</x:v>
       </x:c>
       <x:c r="C9" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_manager.c:68
-LTD_MAIN_CPU2/Application/Src/fault_recovery.c:46
-LTD_MAIN_CPU2/Application/Src/measure_zero.c:68
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:881
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:888
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1021
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:1028</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:71
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:101
+LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:142</x:v>
       </x:c>
       <x:c r="D9" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E9" s="72" t="str">
-        <x:v>电机驱动配置丢失</x:v>
+        <x:v>电机驱动过温关断</x:v>
       </x:c>
       <x:c r="F9" s="72" t="str">
-        <x:v>TMC5130运行期复位或关键配置丢失</x:v>
+        <x:v>电机驱动已过温关断</x:v>
       </x:c>
       <x:c r="G9" s="72" t="str">
-        <x:v>电机驱动配置丢失</x:v>
+        <x:v>电机驱动过温停止</x:v>
       </x:c>
       <x:c r="H9" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -7856,7 +7856,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K9" s="72" t="str">
-        <x:v>1-3 电机驱动异常重启</x:v>
+        <x:v>1-7 电机驱动器报警</x:v>
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9"/>
@@ -7871,39 +7871,42 @@
     </x:row>
     <x:row r="10" ht="78" customHeight="1">
       <x:c r="A10" s="73" t="str">
-        <x:v>11-20</x:v>
+        <x:v>11-18</x:v>
       </x:c>
       <x:c r="B10" s="68" t="str">
-        <x:v>MOTOR_STALL_ERROR</x:v>
+        <x:v>MOTOR_RUN_TIMEOUT</x:v>
       </x:c>
       <x:c r="C10" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:72
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:97
-LTD_MAIN_CPU2/BSP/Peripherals/src/TMC5130.c:148</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/fault_recovery.c:50
+LTD_MAIN_CPU2/Application/Src/measure_zero.c:72
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2028
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2352
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2355
+LTD_MAIN_CPU2/Services/MotorControl/motor_ctrl_motion_api.c:2362</x:v>
       </x:c>
       <x:c r="D10" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E10" s="68" t="str">
-        <x:v>电机堵转</x:v>
+        <x:v>电机运行超时</x:v>
       </x:c>
       <x:c r="F10" s="68" t="str">
-        <x:v>电机堵转或负载阻力过大</x:v>
+        <x:v>电机整段运行超时</x:v>
       </x:c>
       <x:c r="G10" s="68" t="str">
-        <x:v>电机运行阻力大</x:v>
+        <x:v>电机运行超时</x:v>
       </x:c>
       <x:c r="H10" s="68" t="str">
-        <x:v>按现有命令白名单和故障恢复边界处理</x:v>
+        <x:v>可在部件状态恢复后按命令白名单重跑</x:v>
       </x:c>
       <x:c r="I10" s="68" t="str">
         <x:v>来源、名称、原因和CPU3显示均已覆盖</x:v>
       </x:c>
       <x:c r="J10" s="68" t="str">
-        <x:v>台架核对编号、日志、停机和恢复行为</x:v>
+        <x:v>故障注入11-18，核对屏幕编号、日志原因、停机和恢复口径</x:v>
       </x:c>
       <x:c r="K10" s="68" t="str">
-        <x:v>1-11 电机堵转</x:v>
+        <x:v>1-10 输入步进数错误</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10"/>
@@ -7918,7 +7921,7 @@
     </x:row>
     <x:row r="11" ht="93" customHeight="1">
       <x:c r="A11" s="74" t="str">
-        <x:v>11-21</x:v>
+        <x:v>11-19</x:v>
       </x:c>
       <x:c r="B11" s="72" t="str">
         <x:v>MOTOR_PHASE_SHORT_ERROR</x:v>
@@ -7966,7 +7969,7 @@
     </x:row>
     <x:row r="12" ht="93" customHeight="1">
       <x:c r="A12" s="73" t="str">
-        <x:v>11-22</x:v>
+        <x:v>11-20</x:v>
       </x:c>
       <x:c r="B12" s="68" t="str">
         <x:v>MOTOR_PHASE_OPEN_ERROR</x:v>
@@ -8014,7 +8017,7 @@
     </x:row>
     <x:row r="13" ht="78" customHeight="1">
       <x:c r="A13" s="74" t="str">
-        <x:v>11-23</x:v>
+        <x:v>11-21</x:v>
       </x:c>
       <x:c r="B13" s="72" t="str">
         <x:v>MOTOR_DRIVER_OVERTEMP_WARNING</x:v>
@@ -8061,7 +8064,7 @@
     </x:row>
     <x:row r="14" ht="110" customHeight="1">
       <x:c r="A14" s="73" t="str">
-        <x:v>11-24</x:v>
+        <x:v>11-22</x:v>
       </x:c>
       <x:c r="B14" s="68" t="str">
         <x:v>MOTOR_DRIVER_NOT_INITIALIZED</x:v>
@@ -8111,7 +8114,7 @@
     </x:row>
     <x:row r="15" ht="110" customHeight="1">
       <x:c r="A15" s="74" t="str">
-        <x:v>11-25</x:v>
+        <x:v>11-23</x:v>
       </x:c>
       <x:c r="B15" s="72" t="str">
         <x:v>MOTOR_STOP_WAIT_TIMEOUT</x:v>
@@ -8161,7 +8164,7 @@
     </x:row>
     <x:row r="16" ht="110" customHeight="1">
       <x:c r="A16" s="73" t="str">
-        <x:v>11-26</x:v>
+        <x:v>11-24</x:v>
       </x:c>
       <x:c r="B16" s="68" t="str">
         <x:v>MOTOR_ARRIVAL_WAIT_TIMEOUT</x:v>
@@ -10591,7 +10594,7 @@
     </x:row>
     <x:row r="68" ht="78" customHeight="1">
       <x:c r="A68" s="73" t="str">
-        <x:v>14-12</x:v>
+        <x:v>14-11</x:v>
       </x:c>
       <x:c r="B68" s="68" t="str">
         <x:v>MEASUREMENT_ZERO_REPEAT_FAIL</x:v>
@@ -10637,7 +10640,7 @@
     </x:row>
     <x:row r="69" ht="110" customHeight="1">
       <x:c r="A69" s="74" t="str">
-        <x:v>14-13</x:v>
+        <x:v>14-12</x:v>
       </x:c>
       <x:c r="B69" s="72" t="str">
         <x:v>POSITION_DATA_INVALID</x:v>
@@ -10685,7 +10688,7 @@
     </x:row>
     <x:row r="70" ht="63" customHeight="1">
       <x:c r="A70" s="73" t="str">
-        <x:v>14-14</x:v>
+        <x:v>14-13</x:v>
       </x:c>
       <x:c r="B70" s="68" t="str">
         <x:v>POSITION_TARGET_OVERRUN</x:v>
@@ -10730,7 +10733,7 @@
     </x:row>
     <x:row r="71" ht="78" customHeight="1">
       <x:c r="A71" s="74" t="str">
-        <x:v>14-15</x:v>
+        <x:v>14-14</x:v>
       </x:c>
       <x:c r="B71" s="72" t="str">
         <x:v>POSITION_ARRIVAL_DEVIATION</x:v>
@@ -10776,7 +10779,7 @@
     </x:row>
     <x:row r="72" ht="110" customHeight="1">
       <x:c r="A72" s="73" t="str">
-        <x:v>14-16</x:v>
+        <x:v>14-15</x:v>
       </x:c>
       <x:c r="B72" s="68" t="str">
         <x:v>POSITION_MOTOR_NOT_STOPPED</x:v>
@@ -10957,32 +10960,25 @@
     </x:row>
     <x:row r="76" ht="108" customHeight="1">
       <x:c r="A76" s="73" t="str">
-        <x:v>15-18</x:v>
+        <x:v>15-17</x:v>
       </x:c>
       <x:c r="B76" s="68" t="str">
-        <x:v>MEASUREMENT_OILLEVEL_LOW</x:v>
+        <x:v>MEASUREMENT_DENSITY_LEVEL_TIMEOUT</x:v>
       </x:c>
       <x:c r="C76" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:954
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1471
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1497
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1549
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1797
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1933
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1949
-LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:375</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:597</x:v>
       </x:c>
       <x:c r="D76" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E76" s="68" t="str">
-        <x:v>下行未找到液位</x:v>
+        <x:v>密度找液位超时</x:v>
       </x:c>
       <x:c r="F76" s="68" t="str">
-        <x:v>下行测量未找到液位</x:v>
+        <x:v>密度闭环找液位超时</x:v>
       </x:c>
       <x:c r="G76" s="68" t="str">
-        <x:v>下行未找到液位</x:v>
+        <x:v>密度找液位超时</x:v>
       </x:c>
       <x:c r="H76" s="68" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -10994,7 +10990,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K76" s="68" t="str">
-        <x:v>6-4 油位太低；下行到盲区未检测到油。</x:v>
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="L76"/>
       <x:c r="M76"/>
@@ -11009,27 +11005,32 @@
     </x:row>
     <x:row r="77" ht="110" customHeight="1">
       <x:c r="A77" s="74" t="str">
-        <x:v>15-19</x:v>
+        <x:v>15-18</x:v>
       </x:c>
       <x:c r="B77" s="72" t="str">
-        <x:v>MEASUREMENT_OILLEVEL_NOTFOUND</x:v>
+        <x:v>MEASUREMENT_OILLEVEL_LOW</x:v>
       </x:c>
       <x:c r="C77" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_density.c:963
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1154
-LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1201</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:954
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1471
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1497
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1549
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1797
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1933
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1949
+LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:375</x:v>
       </x:c>
       <x:c r="D77" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E77" s="72" t="str">
-        <x:v>上行未找到液位</x:v>
+        <x:v>下行未找到液位</x:v>
       </x:c>
       <x:c r="F77" s="72" t="str">
-        <x:v>上行测量未找到液位</x:v>
+        <x:v>下行测量未找到液位</x:v>
       </x:c>
       <x:c r="G77" s="72" t="str">
-        <x:v>上行未找到液位</x:v>
+        <x:v>下行未找到液位</x:v>
       </x:c>
       <x:c r="H77" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -11041,7 +11042,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K77" s="72" t="str">
-        <x:v>6-5 运行到零点位置未找到液位；</x:v>
+        <x:v>6-4 油位太低；下行到盲区未检测到油。</x:v>
       </x:c>
       <x:c r="L77"/>
       <x:c r="M77"/>
@@ -11056,28 +11057,27 @@
     </x:row>
     <x:row r="78" ht="93" customHeight="1">
       <x:c r="A78" s="73" t="str">
-        <x:v>15-20</x:v>
+        <x:v>15-19</x:v>
       </x:c>
       <x:c r="B78" s="68" t="str">
-        <x:v>MEASUREMENT_WEIGHT_DOWN_FAIL</x:v>
+        <x:v>MEASUREMENT_OILLEVEL_NOTFOUND</x:v>
       </x:c>
       <x:c r="C78" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1354
-LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:85
-LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:544
-LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:642</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_density.c:963
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1154
+LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1201</x:v>
       </x:c>
       <x:c r="D78" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E78" s="68" t="str">
-        <x:v>下行寻重失败</x:v>
+        <x:v>上行未找到液位</x:v>
       </x:c>
       <x:c r="F78" s="68" t="str">
-        <x:v>下行寻重失败</x:v>
+        <x:v>上行测量未找到液位</x:v>
       </x:c>
       <x:c r="G78" s="68" t="str">
-        <x:v>下行寻重失败</x:v>
+        <x:v>上行未找到液位</x:v>
       </x:c>
       <x:c r="H78" s="68" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -11089,7 +11089,7 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K78" s="68" t="str">
-        <x:v>4-4 测量罐底，下行到达罐高+最大下行位置；</x:v>
+        <x:v>6-5 运行到零点位置未找到液位；</x:v>
       </x:c>
       <x:c r="L78"/>
       <x:c r="M78"/>
@@ -11104,25 +11104,28 @@
     </x:row>
     <x:row r="79" ht="78" customHeight="1">
       <x:c r="A79" s="74" t="str">
-        <x:v>15-21</x:v>
+        <x:v>15-20</x:v>
       </x:c>
       <x:c r="B79" s="72" t="str">
-        <x:v>MEASUREMENT_WEIGHT_UP_FAIL</x:v>
+        <x:v>MEASUREMENT_WEIGHT_DOWN_FAIL</x:v>
       </x:c>
       <x:c r="C79" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_zero.c:338</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:1354
+LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:85
+LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:544
+LTD_MAIN_CPU2/Application/Src/measure_tank_height.c:642</x:v>
       </x:c>
       <x:c r="D79" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E79" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
+        <x:v>下行寻重失败</x:v>
       </x:c>
       <x:c r="F79" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
+        <x:v>下行寻重失败</x:v>
       </x:c>
       <x:c r="G79" s="72" t="str">
-        <x:v>上行寻重失败</x:v>
+        <x:v>下行寻重失败</x:v>
       </x:c>
       <x:c r="H79" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -11134,17 +11137,52 @@
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
       <x:c r="K79" s="72" t="str">
-        <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
+        <x:v>4-4 测量罐底，下行到达罐高+最大下行位置；</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="78" customHeight="1">
       <x:c r="A80" s="73" t="str">
+        <x:v>15-21</x:v>
+      </x:c>
+      <x:c r="B80" s="68" t="str">
+        <x:v>MEASUREMENT_WEIGHT_UP_FAIL</x:v>
+      </x:c>
+      <x:c r="C80" s="68" t="str">
+        <x:v>LTD_MAIN_CPU2/Application/Src/measure_zero.c:338</x:v>
+      </x:c>
+      <x:c r="D80" s="68" t="str">
+        <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
+      </x:c>
+      <x:c r="E80" s="68" t="str">
+        <x:v>上行寻重失败</x:v>
+      </x:c>
+      <x:c r="F80" s="68" t="str">
+        <x:v>上行寻重失败</x:v>
+      </x:c>
+      <x:c r="G80" s="68" t="str">
+        <x:v>上行寻重失败</x:v>
+      </x:c>
+      <x:c r="H80" s="68" t="str">
+        <x:v>按现有命令白名单和故障恢复边界处理</x:v>
+      </x:c>
+      <x:c r="I80" s="68" t="str">
+        <x:v>来源、名称、原因和CPU3显示均已覆盖</x:v>
+      </x:c>
+      <x:c r="J80" s="68" t="str">
+        <x:v>台架核对编号、日志、停机和恢复行为</x:v>
+      </x:c>
+      <x:c r="K80" s="68" t="str">
+        <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="78" customHeight="1">
+      <x:c r="A81" s="74" t="str">
         <x:v>15-22</x:v>
       </x:c>
-      <x:c r="B80" s="68" t="str">
+      <x:c r="B81" s="72" t="str">
         <x:v>MEASUREMENT_WATERLEVEL_LOW</x:v>
       </x:c>
-      <x:c r="C80" s="68" t="str">
+      <x:c r="C81" s="72" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:273
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:333
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:578
@@ -11152,91 +11190,56 @@
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:660
 LTD_MAIN_CPU2/Application/Src/measure_waterLevel.c:863</x:v>
       </x:c>
-      <x:c r="D80" s="68" t="str">
+      <x:c r="D81" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
-      <x:c r="E80" s="68" t="str">
+      <x:c r="E81" s="72" t="str">
         <x:v>下行未找到水位</x:v>
       </x:c>
-      <x:c r="F80" s="68" t="str">
+      <x:c r="F81" s="72" t="str">
         <x:v>下行测量未找到水位</x:v>
       </x:c>
-      <x:c r="G80" s="68" t="str">
+      <x:c r="G81" s="72" t="str">
         <x:v>下行未找到水位</x:v>
       </x:c>
-      <x:c r="H80" s="68" t="str">
+      <x:c r="H81" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
       </x:c>
-      <x:c r="I80" s="68" t="str">
+      <x:c r="I81" s="72" t="str">
         <x:v>来源、名称、原因和CPU3显示均已覆盖</x:v>
       </x:c>
-      <x:c r="J80" s="68" t="str">
+      <x:c r="J81" s="72" t="str">
         <x:v>台架核对编号、日志、停机和恢复行为</x:v>
       </x:c>
-      <x:c r="K80" s="68" t="str">
+      <x:c r="K81" s="72" t="str">
         <x:v>6-3 1.找水位时上行到了零点；</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="78" customHeight="1">
-      <x:c r="A81" s="74" t="str">
+    <x:row r="82" ht="78" customHeight="1">
+      <x:c r="A82" s="73" t="str">
         <x:v>15-23</x:v>
       </x:c>
-      <x:c r="B81" s="72" t="str">
+      <x:c r="B82" s="68" t="str">
         <x:v>MEASUREMENT_DENSITY_NO_VALID_POINT</x:v>
       </x:c>
-      <x:c r="C81" s="72" t="str">
+      <x:c r="C82" s="68" t="str">
         <x:v>LTD_MAIN_CPU2/Application/Src/measure_density.c:352
 LTD_MAIN_CPU2/Application/Src/measure_density.c:959
 LTD_MAIN_CPU2/Application/Src/measure_density.c:1490
 LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:456
 LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:586</x:v>
       </x:c>
-      <x:c r="D81" s="72" t="str">
-        <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
-      </x:c>
-      <x:c r="E81" s="72" t="str">
-        <x:v>密度测量无有效点</x:v>
-      </x:c>
-      <x:c r="F81" s="72" t="str">
-        <x:v>密度分布测量无有效测点</x:v>
-      </x:c>
-      <x:c r="G81" s="72" t="str">
-        <x:v>密度测量无有效点</x:v>
-      </x:c>
-      <x:c r="H81" s="72" t="str">
-        <x:v>按现有命令白名单和故障恢复边界处理</x:v>
-      </x:c>
-      <x:c r="I81" s="72" t="str">
-        <x:v>来源、名称、原因和CPU3显示均已覆盖</x:v>
-      </x:c>
-      <x:c r="J81" s="72" t="str">
-        <x:v>台架核对编号、日志、停机和恢复行为</x:v>
-      </x:c>
-      <x:c r="K81" s="72" t="str">
-        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="78" customHeight="1">
-      <x:c r="A82" s="73" t="str">
-        <x:v>15-24</x:v>
-      </x:c>
-      <x:c r="B82" s="68" t="str">
-        <x:v>MEASUREMENT_DENSITY_SURFACE_NOTFOUND</x:v>
-      </x:c>
-      <x:c r="C82" s="68" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:581</x:v>
-      </x:c>
       <x:c r="D82" s="68" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E82" s="68" t="str">
-        <x:v>密度测量未找到油面</x:v>
+        <x:v>密度测量无有效点</x:v>
       </x:c>
       <x:c r="F82" s="68" t="str">
-        <x:v>密度分布测量未找到油面</x:v>
+        <x:v>密度分布测量无有效测点</x:v>
       </x:c>
       <x:c r="G82" s="68" t="str">
-        <x:v>密度测量未找到油面</x:v>
+        <x:v>密度测量无有效点</x:v>
       </x:c>
       <x:c r="H82" s="68" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -11253,25 +11256,25 @@
     </x:row>
     <x:row r="83" ht="110" customHeight="1">
       <x:c r="A83" s="74" t="str">
-        <x:v>15-25</x:v>
+        <x:v>15-24</x:v>
       </x:c>
       <x:c r="B83" s="72" t="str">
-        <x:v>MEASUREMENT_DENSITY_LEVEL_TIMEOUT</x:v>
+        <x:v>MEASUREMENT_DENSITY_SURFACE_NOTFOUND</x:v>
       </x:c>
       <x:c r="C83" s="72" t="str">
-        <x:v>LTD_MAIN_CPU2/Application/Src/measure_oilLevel.c:597</x:v>
+        <x:v>LTD_MAIN_CPU2/Application/Src/wartsila_density_measurement.c:581</x:v>
       </x:c>
       <x:c r="D83" s="72" t="str">
         <x:v>具体故障码沿返回链保留，最终由业务流程或统一故障管理置错</x:v>
       </x:c>
       <x:c r="E83" s="72" t="str">
-        <x:v>密度找液位超时</x:v>
+        <x:v>密度测量未找到油面</x:v>
       </x:c>
       <x:c r="F83" s="72" t="str">
-        <x:v>密度闭环找液位超时</x:v>
+        <x:v>密度分布测量未找到油面</x:v>
       </x:c>
       <x:c r="G83" s="72" t="str">
-        <x:v>密度找液位超时</x:v>
+        <x:v>密度测量未找到油面</x:v>
       </x:c>
       <x:c r="H83" s="72" t="str">
         <x:v>按现有命令白名单和故障恢复边界处理</x:v>
@@ -11288,7 +11291,7 @@
     </x:row>
     <x:row r="84" ht="110" customHeight="1">
       <x:c r="A84" s="73" t="str">
-        <x:v>15-26</x:v>
+        <x:v>15-25</x:v>
       </x:c>
       <x:c r="B84" s="68" t="str">
         <x:v>MEASUREMENT_FREQUENCY_LEVEL_TIMEOUT</x:v>
@@ -11323,7 +11326,7 @@
     </x:row>
     <x:row r="85" ht="108" customHeight="1">
       <x:c r="A85" s="74" t="str">
-        <x:v>15-27</x:v>
+        <x:v>15-26</x:v>
       </x:c>
       <x:c r="B85" s="72" t="str">
         <x:v>MEASUREMENT_BOTTOM_RELEASE_FAIL</x:v>
@@ -11358,7 +11361,7 @@
     </x:row>
     <x:row r="86" ht="108" customHeight="1">
       <x:c r="A86" s="73" t="str">
-        <x:v>15-28</x:v>
+        <x:v>15-27</x:v>
       </x:c>
       <x:c r="B86" s="68" t="str">
         <x:v>MEASUREMENT_TANK_HEIGHT_NOT_CONFIGURED</x:v>
@@ -11394,7 +11397,7 @@
     </x:row>
     <x:row r="87" ht="110" customHeight="1">
       <x:c r="A87" s="74" t="str">
-        <x:v>15-29</x:v>
+        <x:v>15-28</x:v>
       </x:c>
       <x:c r="B87" s="72" t="str">
         <x:v>MEASUREMENT_WATER_CALIBRATION_NOT_CONFIGURED</x:v>
@@ -11430,7 +11433,7 @@
     </x:row>
     <x:row r="88" ht="48" customHeight="1">
       <x:c r="A88" s="73" t="str">
-        <x:v>15-31</x:v>
+        <x:v>15-29</x:v>
       </x:c>
       <x:c r="B88" s="68" t="str">
         <x:v>MEASUREMENT_DENSITY_PLAN_INVALID</x:v>
@@ -11472,7 +11475,7 @@
     </x:row>
     <x:row r="89" ht="48" customHeight="1">
       <x:c r="A89" s="74" t="str">
-        <x:v>15-32</x:v>
+        <x:v>15-30</x:v>
       </x:c>
       <x:c r="B89" s="72" t="str">
         <x:v>MEASUREMENT_TANK_HEIGHT_RESULT_INVALID</x:v>
@@ -11508,7 +11511,7 @@
     </x:row>
     <x:row r="90" ht="78" customHeight="1">
       <x:c r="A90" s="73" t="str">
-        <x:v>15-33</x:v>
+        <x:v>15-31</x:v>
       </x:c>
       <x:c r="B90" s="68" t="str">
         <x:v>MEASUREMENT_WATER_CALC_OUT_OF_RANGE</x:v>
@@ -12004,7 +12007,7 @@
     </x:row>
     <x:row r="103" ht="63" customHeight="1">
       <x:c r="A103" s="74" t="str">
-        <x:v>18-10</x:v>
+        <x:v>18-9</x:v>
       </x:c>
       <x:c r="B103" s="72" t="str">
         <x:v>AD5421_INTERNAL_COMM_ERROR</x:v>
@@ -12041,7 +12044,7 @@
     </x:row>
     <x:row r="104" ht="108" customHeight="1">
       <x:c r="A104" s="73" t="str">
-        <x:v>18-11</x:v>
+        <x:v>18-10</x:v>
       </x:c>
       <x:c r="B104" s="68" t="str">
         <x:v>AD5421_LOOP_CURRENT_HIGH</x:v>
@@ -12078,7 +12081,7 @@
     </x:row>
     <x:row r="105" ht="110" customHeight="1">
       <x:c r="A105" s="74" t="str">
-        <x:v>18-12</x:v>
+        <x:v>18-11</x:v>
       </x:c>
       <x:c r="B105" s="72" t="str">
         <x:v>AD5421_LOOP_CURRENT_LOW</x:v>
@@ -12115,7 +12118,7 @@
     </x:row>
     <x:row r="106" ht="63" customHeight="1">
       <x:c r="A106" s="73" t="str">
-        <x:v>18-13</x:v>
+        <x:v>18-12</x:v>
       </x:c>
       <x:c r="B106" s="68" t="str">
         <x:v>AD5421_LOOP_VOLTAGE_LOW</x:v>
@@ -12152,7 +12155,7 @@
     </x:row>
     <x:row r="107" ht="57" customHeight="1">
       <x:c r="A107" s="99" t="str">
-        <x:v>18-14</x:v>
+        <x:v>18-13</x:v>
       </x:c>
       <x:c r="B107" s="99" t="str">
         <x:v>AD5421_SPI_TRANSFER_ERROR</x:v>
@@ -12194,7 +12197,7 @@
     </x:row>
     <x:row r="108" ht="57" customHeight="1">
       <x:c r="A108" s="99" t="str">
-        <x:v>18-15</x:v>
+        <x:v>18-14</x:v>
       </x:c>
       <x:c r="B108" s="99" t="str">
         <x:v>AD5421_ACCESS_BUSY</x:v>
@@ -12235,7 +12238,7 @@
     </x:row>
     <x:row r="109" ht="57" customHeight="1">
       <x:c r="A109" s="99" t="str">
-        <x:v>18-16</x:v>
+        <x:v>18-15</x:v>
       </x:c>
       <x:c r="B109" s="99" t="str">
         <x:v>AD5421_OVERTEMP_SHUTDOWN</x:v>
@@ -12274,7 +12277,7 @@
     </x:row>
     <x:row r="110" ht="57" customHeight="1">
       <x:c r="A110" s="99" t="str">
-        <x:v>18-17</x:v>
+        <x:v>18-16</x:v>
       </x:c>
       <x:c r="B110" s="99" t="str">
         <x:v>AD5421_OVERTEMP_WARNING</x:v>
@@ -12936,7 +12939,7 @@
     </x:row>
     <x:row r="128" ht="57" customHeight="1">
       <x:c r="A128" s="99" t="str">
-        <x:v>22-4</x:v>
+        <x:v>22-1</x:v>
       </x:c>
       <x:c r="B128" s="99" t="str">
         <x:v>SYSTEM_BUFFER_CAPACITY_ERROR</x:v>
@@ -12974,7 +12977,7 @@
     </x:row>
     <x:row r="129" ht="57" customHeight="1">
       <x:c r="A129" s="99" t="str">
-        <x:v>22-5</x:v>
+        <x:v>22-2</x:v>
       </x:c>
       <x:c r="B129" s="99" t="str">
         <x:v>SYSTEM_CALL_CONDITION_ERROR</x:v>
@@ -13016,7 +13019,7 @@
     </x:row>
     <x:row r="130" ht="57" customHeight="1">
       <x:c r="A130" s="99" t="str">
-        <x:v>22-6</x:v>
+        <x:v>22-3</x:v>
       </x:c>
       <x:c r="B130" s="99" t="str">
         <x:v>SYSTEM_CALCULATION_ERROR</x:v>
@@ -13091,13 +13094,13 @@
         <x:v>故障项目</x:v>
       </x:c>
       <x:c r="C2" s="97" t="n">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D2" s="92" t="str">
-        <x:v>129个共享故障 + 1个CPU3本机故障</x:v>
+        <x:v>129个共享故障 + 2个CPU3本机故障</x:v>
       </x:c>
       <x:c r="E2" s="92" t="str">
-        <x:v>发布时补齐首个适用CPU2版本</x:v>
+        <x:v>已随CPU2 V1.28.0.0 / CPU3 V1.26.0.0发布；后续按CPU2版本选表</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="38" customHeight="1">
@@ -13108,10 +13111,10 @@
         <x:v>使用中</x:v>
       </x:c>
       <x:c r="C3" s="98" t="n">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D3" s="96" t="str">
-        <x:v>共享使用中126项 + CPU3本机1项</x:v>
+        <x:v>共享使用中126项 + CPU3本机2项</x:v>
       </x:c>
       <x:c r="E3" s="96" t="str">
         <x:v>按调用点和台架逐码验证</x:v>
@@ -13142,13 +13145,13 @@
         <x:v>DEVICE_PROTOCOL_VERSION</x:v>
       </x:c>
       <x:c r="C5" s="98" t="n">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="96" t="str">
-        <x:v>当前开发版内继续细化故障码，协议19尚未正式发布</x:v>
+        <x:v>现行故障码重排已随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23正式发布；CPU2 V1.27.0.0按协议21历史页解释</x:v>
       </x:c>
       <x:c r="E5" s="96" t="str">
-        <x:v>CPU2和CPU3成对发布</x:v>
+        <x:v>双端已按协议23成对发布；协议21/22/23禁止混搭</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -13156,16 +13159,16 @@
         <x:v>历史归档</x:v>
       </x:c>
       <x:c r="B6" s="97" t="str">
-        <x:v>CPU2历史故障项目</x:v>
-      </x:c>
-      <x:c r="C6" s="97" t="n">
-        <x:v>64</x:v>
+        <x:v>CPU2历史故障页</x:v>
+      </x:c>
+      <x:c r="C6" s="97" t="str">
+        <x:v>V1.27 / V1.25～V1.26</x:v>
       </x:c>
       <x:c r="D6" s="92" t="str">
-        <x:v>CPU2 V1.25.0.0～V1.26.0.0使用</x:v>
+        <x:v>V1.27页130项；V1.25.0.0～V1.26.0.0页64项</x:v>
       </x:c>
       <x:c r="E6" s="92" t="str">
-        <x:v>历史编号永久冻结</x:v>
+        <x:v>按CPU2程序版本查询；后续版本允许复用编号</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
@@ -13315,7 +13318,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="96" t="str">
-        <x:v>CPU2共享；另有CPU3本机20-7</x:v>
+        <x:v>CPU2共享；另有CPU3本机20-7、20-13</x:v>
       </x:c>
       <x:c r="E15" s="96" t="str">
         <x:v>按CPU2/CPU3各自程序版本维护</x:v>
@@ -13369,7 +13372,7 @@
         <x:v>双端定义、名称、原因和显示覆盖</x:v>
       </x:c>
       <x:c r="E18" s="92" t="str">
-        <x:v>软件复验已完成；下一步执行台架故障注入和协议混搭验证</x:v>
+        <x:v>静态检查已完成；下一步执行台架故障注入和协议混搭验证</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
@@ -26234,7 +26237,7 @@
     </x:row>
     <x:row r="194" ht="42" customHeight="1">
       <x:c r="A194" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B194" s="99" t="str">
         <x:v>11-18</x:v>
@@ -26255,12 +26258,12 @@
         <x:v>1-10 输入步进数错误</x:v>
       </x:c>
       <x:c r="H194" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="42" customHeight="1">
       <x:c r="A195" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B195" s="99" t="str">
         <x:v>11-18</x:v>
@@ -26281,12 +26284,12 @@
         <x:v>1-10 输入步进数错误</x:v>
       </x:c>
       <x:c r="H195" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="42" customHeight="1">
       <x:c r="A196" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B196" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26307,12 +26310,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H196" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="42" customHeight="1">
       <x:c r="A197" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B197" s="99" t="str">
         <x:v>13-32</x:v>
@@ -26333,12 +26336,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H197" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="42" customHeight="1">
       <x:c r="A198" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B198" s="99" t="str">
         <x:v>13-33</x:v>
@@ -26359,12 +26362,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H198" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="42" customHeight="1">
       <x:c r="A199" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B199" s="99" t="str">
         <x:v>13-34</x:v>
@@ -26385,12 +26388,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H199" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="42" customHeight="1">
       <x:c r="A200" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B200" s="99" t="str">
         <x:v>13-35</x:v>
@@ -26411,12 +26414,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H200" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="42" customHeight="1">
       <x:c r="A201" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B201" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26437,12 +26440,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H201" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="42" customHeight="1">
       <x:c r="A202" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B202" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26463,12 +26466,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H202" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="42" customHeight="1">
       <x:c r="A203" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B203" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26489,12 +26492,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H203" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="42" customHeight="1">
       <x:c r="A204" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B204" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26515,12 +26518,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H204" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="42" customHeight="1">
       <x:c r="A205" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B205" s="99" t="str">
         <x:v>13-31</x:v>
@@ -26541,12 +26544,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H205" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="42" customHeight="1">
       <x:c r="A206" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B206" s="99" t="str">
         <x:v>13-32</x:v>
@@ -26567,12 +26570,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H206" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="42" customHeight="1">
       <x:c r="A207" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B207" s="99" t="str">
         <x:v>13-32</x:v>
@@ -26593,12 +26596,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H207" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="42" customHeight="1">
       <x:c r="A208" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B208" s="99" t="str">
         <x:v>13-32</x:v>
@@ -26619,12 +26622,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H208" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="42" customHeight="1">
       <x:c r="A209" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B209" s="99" t="str">
         <x:v>13-33</x:v>
@@ -26645,12 +26648,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H209" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="42" customHeight="1">
       <x:c r="A210" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B210" s="99" t="str">
         <x:v>13-33</x:v>
@@ -26671,12 +26674,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H210" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="42" customHeight="1">
       <x:c r="A211" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B211" s="99" t="str">
         <x:v>13-33</x:v>
@@ -26697,12 +26700,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H211" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="42" customHeight="1">
       <x:c r="A212" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B212" s="99" t="str">
         <x:v>13-33</x:v>
@@ -26723,12 +26726,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H212" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="42" customHeight="1">
       <x:c r="A213" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B213" s="99" t="str">
         <x:v>13-34</x:v>
@@ -26749,12 +26752,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H213" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="42" customHeight="1">
       <x:c r="A214" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B214" s="99" t="str">
         <x:v>13-34</x:v>
@@ -26775,12 +26778,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H214" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="42" customHeight="1">
       <x:c r="A215" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B215" s="99" t="str">
         <x:v>13-35</x:v>
@@ -26801,12 +26804,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H215" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="42" customHeight="1">
       <x:c r="A216" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B216" s="99" t="str">
         <x:v>13-35</x:v>
@@ -26827,12 +26830,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H216" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="42" customHeight="1">
       <x:c r="A217" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B217" s="99" t="str">
         <x:v>13-35</x:v>
@@ -26853,12 +26856,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H217" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="42" customHeight="1">
       <x:c r="A218" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B218" s="99" t="str">
         <x:v>13-35</x:v>
@@ -26879,12 +26882,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H218" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="42" customHeight="1">
       <x:c r="A219" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B219" s="99" t="str">
         <x:v>15-28</x:v>
@@ -26905,12 +26908,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H219" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="42" customHeight="1">
       <x:c r="A220" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B220" s="99" t="str">
         <x:v>15-29</x:v>
@@ -26931,12 +26934,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H220" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="42" customHeight="1">
       <x:c r="A221" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B221" s="99" t="str">
         <x:v>15-28</x:v>
@@ -26957,12 +26960,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H221" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="42" customHeight="1">
       <x:c r="A222" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B222" s="99" t="str">
         <x:v>15-29</x:v>
@@ -26983,12 +26986,12 @@
         <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
       </x:c>
       <x:c r="H222" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="42" customHeight="1">
       <x:c r="A223" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B223" s="99" t="str">
         <x:v>17-1</x:v>
@@ -27009,12 +27012,12 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="H223" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="42" customHeight="1">
       <x:c r="A224" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B224" s="99" t="str">
         <x:v>17-1</x:v>
@@ -27035,12 +27038,12 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="H224" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="42" customHeight="1">
       <x:c r="A225" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B225" s="99" t="str">
         <x:v>17-1</x:v>
@@ -27061,12 +27064,12 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="H225" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="42" customHeight="1">
       <x:c r="A226" s="99" t="str">
-        <x:v>协议19开发版细化</x:v>
+        <x:v>协议19细化→协议21发布</x:v>
       </x:c>
       <x:c r="B226" s="99" t="str">
         <x:v>17-1</x:v>
@@ -27087,7 +27090,839 @@
         <x:v>7-1 主控板中存储器的参数异常</x:v>
       </x:c>
       <x:c r="H226" s="99" t="str">
-        <x:v>当前开发版调整；正式发布后按CPU2程序版本选表，CPU2 V1.26.0.0及更早按历史页解释</x:v>
+        <x:v>已随CPU2 V1.27.0.0 / CPU3 V1.25.0.0、共享协议21发布；CPU2 V1.26.0.0及更早按历史页解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="25.5" customHeight="1">
+      <x:c r="A227" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>11-19</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>11-3</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
+        <x:v>MOTOR_TMC_CONFIG_LOST</x:v>
+      </x:c>
+      <x:c r="E227" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F227" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G227" t="str">
+        <x:v>1-3 电机驱动异常重启</x:v>
+      </x:c>
+      <x:c r="H227" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="25.5" customHeight="1">
+      <x:c r="A228" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B228" t="str">
+        <x:v>11-20</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>11-11</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
+        <x:v>MOTOR_STALL_ERROR</x:v>
+      </x:c>
+      <x:c r="E228" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F228" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G228" t="str">
+        <x:v>1-11 电机堵转</x:v>
+      </x:c>
+      <x:c r="H228" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="25.5" customHeight="1">
+      <x:c r="A229" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B229" t="str">
+        <x:v>11-21</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>11-19</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
+        <x:v>MOTOR_PHASE_SHORT_ERROR</x:v>
+      </x:c>
+      <x:c r="E229" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F229" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G229" t="str">
+        <x:v>1-15 电机芯片报警</x:v>
+      </x:c>
+      <x:c r="H229" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="25.5" customHeight="1">
+      <x:c r="A230" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B230" t="str">
+        <x:v>11-22</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>11-20</x:v>
+      </x:c>
+      <x:c r="D230" t="str">
+        <x:v>MOTOR_PHASE_OPEN_ERROR</x:v>
+      </x:c>
+      <x:c r="E230" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F230" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G230" t="str">
+        <x:v>1-15 电机芯片报警</x:v>
+      </x:c>
+      <x:c r="H230" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="25.5" customHeight="1">
+      <x:c r="A231" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B231" t="str">
+        <x:v>11-23</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>11-21</x:v>
+      </x:c>
+      <x:c r="D231" t="str">
+        <x:v>MOTOR_DRIVER_OVERTEMP_WARNING</x:v>
+      </x:c>
+      <x:c r="E231" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F231" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G231" t="str">
+        <x:v>1-7 电机驱动器报警</x:v>
+      </x:c>
+      <x:c r="H231" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="25.5" customHeight="1">
+      <x:c r="A232" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B232" t="str">
+        <x:v>11-24</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>11-22</x:v>
+      </x:c>
+      <x:c r="D232" t="str">
+        <x:v>MOTOR_DRIVER_NOT_INITIALIZED</x:v>
+      </x:c>
+      <x:c r="E232" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F232" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G232" t="str">
+        <x:v>1-3 电机驱动异常重启；1-4 修改电机使能输入状态后无法运行（上限位）</x:v>
+      </x:c>
+      <x:c r="H232" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="25.5" customHeight="1">
+      <x:c r="A233" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B233" t="str">
+        <x:v>11-25</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>11-23</x:v>
+      </x:c>
+      <x:c r="D233" t="str">
+        <x:v>MOTOR_STOP_WAIT_TIMEOUT</x:v>
+      </x:c>
+      <x:c r="E233" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F233" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G233" t="str">
+        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
+      </x:c>
+      <x:c r="H233" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="25.5" customHeight="1">
+      <x:c r="A234" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B234" t="str">
+        <x:v>11-26</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>11-24</x:v>
+      </x:c>
+      <x:c r="D234" t="str">
+        <x:v>MOTOR_ARRIVAL_WAIT_TIMEOUT</x:v>
+      </x:c>
+      <x:c r="E234" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="F234" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G234" t="str">
+        <x:v>1-10 输入步进数错误</x:v>
+      </x:c>
+      <x:c r="H234" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="25.5" customHeight="1">
+      <x:c r="A235" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B235" t="str">
+        <x:v>14-12</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>14-11</x:v>
+      </x:c>
+      <x:c r="D235" t="str">
+        <x:v>MEASUREMENT_ZERO_REPEAT_FAIL</x:v>
+      </x:c>
+      <x:c r="E235" t="str">
+        <x:v>零点与位置检测</x:v>
+      </x:c>
+      <x:c r="F235" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G235" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H235" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="25.5" customHeight="1">
+      <x:c r="A236" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B236" t="str">
+        <x:v>14-13</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>14-12</x:v>
+      </x:c>
+      <x:c r="D236" t="str">
+        <x:v>POSITION_DATA_INVALID</x:v>
+      </x:c>
+      <x:c r="E236" t="str">
+        <x:v>零点与位置检测</x:v>
+      </x:c>
+      <x:c r="F236" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G236" t="str">
+        <x:v>2-10 固定点检测时编码值发生变化；4-9 越过零点位置XXmm报错（1.117以上版本）</x:v>
+      </x:c>
+      <x:c r="H236" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="25.5" customHeight="1">
+      <x:c r="A237" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B237" t="str">
+        <x:v>14-14</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>14-13</x:v>
+      </x:c>
+      <x:c r="D237" t="str">
+        <x:v>POSITION_TARGET_OVERRUN</x:v>
+      </x:c>
+      <x:c r="E237" t="str">
+        <x:v>零点与位置检测</x:v>
+      </x:c>
+      <x:c r="F237" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G237" t="str">
+        <x:v>4-9 越过零点位置XXmm报错（1.117以上版本）</x:v>
+      </x:c>
+      <x:c r="H237" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="25.5" customHeight="1">
+      <x:c r="A238" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B238" t="str">
+        <x:v>14-15</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>14-14</x:v>
+      </x:c>
+      <x:c r="D238" t="str">
+        <x:v>POSITION_ARRIVAL_DEVIATION</x:v>
+      </x:c>
+      <x:c r="E238" t="str">
+        <x:v>零点与位置检测</x:v>
+      </x:c>
+      <x:c r="F238" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G238" t="str">
+        <x:v>5-12 电机步进数和实际运行数差距大，拟合数据不正确；</x:v>
+      </x:c>
+      <x:c r="H238" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="25.5" customHeight="1">
+      <x:c r="A239" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B239" t="str">
+        <x:v>14-16</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>14-15</x:v>
+      </x:c>
+      <x:c r="D239" t="str">
+        <x:v>POSITION_MOTOR_NOT_STOPPED</x:v>
+      </x:c>
+      <x:c r="E239" t="str">
+        <x:v>零点与位置检测</x:v>
+      </x:c>
+      <x:c r="F239" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G239" t="str">
+        <x:v>1-10 输入步进数错误； 下位位置高于当前位置 限制上行时步进数超过零点</x:v>
+      </x:c>
+      <x:c r="H239" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="25.5" customHeight="1">
+      <x:c r="A240" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B240" t="str">
+        <x:v>15-25</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>15-17</x:v>
+      </x:c>
+      <x:c r="D240" t="str">
+        <x:v>MEASUREMENT_DENSITY_LEVEL_TIMEOUT</x:v>
+      </x:c>
+      <x:c r="E240" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F240" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G240" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H240" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="25.5" customHeight="1">
+      <x:c r="A241" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B241" t="str">
+        <x:v>15-26</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>15-25</x:v>
+      </x:c>
+      <x:c r="D241" t="str">
+        <x:v>MEASUREMENT_FREQUENCY_LEVEL_TIMEOUT</x:v>
+      </x:c>
+      <x:c r="E241" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F241" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G241" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H241" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="25.5" customHeight="1">
+      <x:c r="A242" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B242" t="str">
+        <x:v>15-27</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>15-26</x:v>
+      </x:c>
+      <x:c r="D242" t="str">
+        <x:v>MEASUREMENT_BOTTOM_RELEASE_FAIL</x:v>
+      </x:c>
+      <x:c r="E242" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F242" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G242" t="str">
+        <x:v>4-3 测量罐底时上行细找找到零点位置；</x:v>
+      </x:c>
+      <x:c r="H242" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="25.5" customHeight="1">
+      <x:c r="A243" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B243" t="str">
+        <x:v>15-28</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>15-27</x:v>
+      </x:c>
+      <x:c r="D243" t="str">
+        <x:v>MEASUREMENT_TANK_HEIGHT_NOT_CONFIGURED</x:v>
+      </x:c>
+      <x:c r="E243" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F243" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G243" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H243" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="25.5" customHeight="1">
+      <x:c r="A244" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B244" t="str">
+        <x:v>15-29</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>15-28</x:v>
+      </x:c>
+      <x:c r="D244" t="str">
+        <x:v>MEASUREMENT_WATER_CALIBRATION_NOT_CONFIGURED</x:v>
+      </x:c>
+      <x:c r="E244" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F244" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G244" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H244" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="25.5" customHeight="1">
+      <x:c r="A245" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B245" t="str">
+        <x:v>15-31</x:v>
+      </x:c>
+      <x:c r="C245" t="str">
+        <x:v>15-29</x:v>
+      </x:c>
+      <x:c r="D245" t="str">
+        <x:v>MEASUREMENT_DENSITY_PLAN_INVALID</x:v>
+      </x:c>
+      <x:c r="E245" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F245" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G245" t="str">
+        <x:v>5-4 1.进行单点监测或单点测量时，输入的检测位置小于盲区位置或高于罐高。 2.区间测量输入液位区间错误；5-5 密度分布测量或标定液位时，液位值过低； 2.区间测量参数设置最低点要＞（盲区+300）；否侧报错；5-6 1.区间测量参数设置最高点高于罐高。 2.分布测量或每米测量液位高度高于罐高；5-7 密度分布测量点数超过100（加测点过多）</x:v>
+      </x:c>
+      <x:c r="H245" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="25.5" customHeight="1">
+      <x:c r="A246" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B246" t="str">
+        <x:v>15-32</x:v>
+      </x:c>
+      <x:c r="C246" t="str">
+        <x:v>15-30</x:v>
+      </x:c>
+      <x:c r="D246" t="str">
+        <x:v>MEASUREMENT_TANK_HEIGHT_RESULT_INVALID</x:v>
+      </x:c>
+      <x:c r="E246" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F246" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G246" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H246" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="25.5" customHeight="1">
+      <x:c r="A247" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B247" t="str">
+        <x:v>15-33</x:v>
+      </x:c>
+      <x:c r="C247" t="str">
+        <x:v>15-31</x:v>
+      </x:c>
+      <x:c r="D247" t="str">
+        <x:v>MEASUREMENT_WATER_CALC_OUT_OF_RANGE</x:v>
+      </x:c>
+      <x:c r="E247" t="str">
+        <x:v>测量过程</x:v>
+      </x:c>
+      <x:c r="F247" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G247" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H247" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="25.5" customHeight="1">
+      <x:c r="A248" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B248" t="str">
+        <x:v>18-10</x:v>
+      </x:c>
+      <x:c r="C248" t="str">
+        <x:v>18-9</x:v>
+      </x:c>
+      <x:c r="D248" t="str">
+        <x:v>AD5421_INTERNAL_COMM_ERROR</x:v>
+      </x:c>
+      <x:c r="E248" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F248" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G248" t="str">
+        <x:v>8-3 上电自检_电流芯片报警</x:v>
+      </x:c>
+      <x:c r="H248" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="25.5" customHeight="1">
+      <x:c r="A249" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B249" t="str">
+        <x:v>18-11</x:v>
+      </x:c>
+      <x:c r="C249" t="str">
+        <x:v>18-10</x:v>
+      </x:c>
+      <x:c r="D249" t="str">
+        <x:v>AD5421_LOOP_CURRENT_HIGH</x:v>
+      </x:c>
+      <x:c r="E249" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F249" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G249" t="str">
+        <x:v>8-3 上电自检_电流芯片报警；8-6 输入电流对比异常</x:v>
+      </x:c>
+      <x:c r="H249" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="25.5" customHeight="1">
+      <x:c r="A250" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B250" t="str">
+        <x:v>18-12</x:v>
+      </x:c>
+      <x:c r="C250" t="str">
+        <x:v>18-11</x:v>
+      </x:c>
+      <x:c r="D250" t="str">
+        <x:v>AD5421_LOOP_CURRENT_LOW</x:v>
+      </x:c>
+      <x:c r="E250" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F250" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G250" t="str">
+        <x:v>8-3 上电自检_电流芯片报警；8-6 输入电流对比异常</x:v>
+      </x:c>
+      <x:c r="H250" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="25.5" customHeight="1">
+      <x:c r="A251" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B251" t="str">
+        <x:v>18-13</x:v>
+      </x:c>
+      <x:c r="C251" t="str">
+        <x:v>18-12</x:v>
+      </x:c>
+      <x:c r="D251" t="str">
+        <x:v>AD5421_LOOP_VOLTAGE_LOW</x:v>
+      </x:c>
+      <x:c r="E251" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F251" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G251" t="str">
+        <x:v>8-4 设备供电电压异常</x:v>
+      </x:c>
+      <x:c r="H251" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="25.5" customHeight="1">
+      <x:c r="A252" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B252" t="str">
+        <x:v>18-14</x:v>
+      </x:c>
+      <x:c r="C252" t="str">
+        <x:v>18-13</x:v>
+      </x:c>
+      <x:c r="D252" t="str">
+        <x:v>AD5421_SPI_TRANSFER_ERROR</x:v>
+      </x:c>
+      <x:c r="E252" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F252" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G252" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H252" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="25.5" customHeight="1">
+      <x:c r="A253" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B253" t="str">
+        <x:v>18-15</x:v>
+      </x:c>
+      <x:c r="C253" t="str">
+        <x:v>18-14</x:v>
+      </x:c>
+      <x:c r="D253" t="str">
+        <x:v>AD5421_ACCESS_BUSY</x:v>
+      </x:c>
+      <x:c r="E253" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F253" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G253" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H253" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="25.5" customHeight="1">
+      <x:c r="A254" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B254" t="str">
+        <x:v>18-16</x:v>
+      </x:c>
+      <x:c r="C254" t="str">
+        <x:v>18-15</x:v>
+      </x:c>
+      <x:c r="D254" t="str">
+        <x:v>AD5421_OVERTEMP_SHUTDOWN</x:v>
+      </x:c>
+      <x:c r="E254" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F254" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G254" t="str">
+        <x:v>8-8 芯片温度过高</x:v>
+      </x:c>
+      <x:c r="H254" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="25.5" customHeight="1">
+      <x:c r="A255" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B255" t="str">
+        <x:v>18-17</x:v>
+      </x:c>
+      <x:c r="C255" t="str">
+        <x:v>18-16</x:v>
+      </x:c>
+      <x:c r="D255" t="str">
+        <x:v>AD5421_OVERTEMP_WARNING</x:v>
+      </x:c>
+      <x:c r="E255" t="str">
+        <x:v>模拟输出与自检</x:v>
+      </x:c>
+      <x:c r="F255" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G255" t="str">
+        <x:v>8-8 芯片温度过高</x:v>
+      </x:c>
+      <x:c r="H255" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="25.5" customHeight="1">
+      <x:c r="A256" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B256" t="str">
+        <x:v>22-4</x:v>
+      </x:c>
+      <x:c r="C256" t="str">
+        <x:v>22-1</x:v>
+      </x:c>
+      <x:c r="D256" t="str">
+        <x:v>SYSTEM_BUFFER_CAPACITY_ERROR</x:v>
+      </x:c>
+      <x:c r="E256" t="str">
+        <x:v>系统与软件</x:v>
+      </x:c>
+      <x:c r="F256" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G256" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H256" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="25.5" customHeight="1">
+      <x:c r="A257" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B257" t="str">
+        <x:v>22-5</x:v>
+      </x:c>
+      <x:c r="C257" t="str">
+        <x:v>22-2</x:v>
+      </x:c>
+      <x:c r="D257" t="str">
+        <x:v>SYSTEM_CALL_CONDITION_ERROR</x:v>
+      </x:c>
+      <x:c r="E257" t="str">
+        <x:v>系统与软件</x:v>
+      </x:c>
+      <x:c r="F257" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G257" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H257" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="25.5" customHeight="1">
+      <x:c r="A258" t="str">
+        <x:v>协议21→23（协议22开发态）</x:v>
+      </x:c>
+      <x:c r="B258" t="str">
+        <x:v>22-6</x:v>
+      </x:c>
+      <x:c r="C258" t="str">
+        <x:v>22-3</x:v>
+      </x:c>
+      <x:c r="D258" t="str">
+        <x:v>SYSTEM_CALCULATION_ERROR</x:v>
+      </x:c>
+      <x:c r="E258" t="str">
+        <x:v>系统与软件</x:v>
+      </x:c>
+      <x:c r="F258" t="str">
+        <x:v>调整子码</x:v>
+      </x:c>
+      <x:c r="G258" t="str">
+        <x:v>一代无直接同义编号；按二代责任域独立编号</x:v>
+      </x:c>
+      <x:c r="H258" t="str">
+        <x:v>CPU2 V1.27.0.0历史页保留旧编号；该重排随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次发布。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -27166,6 +28001,36 @@
 LTD_DISPLAY_CPU3/Communication/internal/main_board_modbus/cpu2_communicate.c:933</x:v>
       </x:c>
       <x:c r="I2" s="92" t="str">
+        <x:v>不属于CPU2共享故障；按CPU3程序版本确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="100" customHeight="1">
+      <x:c r="A3" s="100" t="str">
+        <x:v>20-13</x:v>
+      </x:c>
+      <x:c r="B3" s="100" t="str">
+        <x:v>0x0014000D</x:v>
+      </x:c>
+      <x:c r="C3" s="100" t="str">
+        <x:v>CPU2_PROFILE_SYNC_FAILED</x:v>
+      </x:c>
+      <x:c r="D3" s="100" t="str">
+        <x:v>CPU3显示单元</x:v>
+      </x:c>
+      <x:c r="E3" s="100" t="str">
+        <x:v>完成锁存有效，但连续三轮或15秒内未取得完成计数、测点数量、结果来源和完成锁存前后一致的完整分布点阵</x:v>
+      </x:c>
+      <x:c r="F3" s="100" t="str">
+        <x:v>完成锁存清除或出现新的完成代际后重新同步；完整点阵提交成功后解除</x:v>
+      </x:c>
+      <x:c r="G3" s="100" t="str">
+        <x:v>分布结果读取失败</x:v>
+      </x:c>
+      <x:c r="H3" s="100" t="str">
+        <x:v>LTD_DISPLAY_CPU3/Communication/internal/main_board_modbus/cpu2_communicate.c:733
+LTD_DISPLAY_CPU3/Communication/internal/main_board_modbus/cpu2_communicate.c:1028</x:v>
+      </x:c>
+      <x:c r="I3" s="100" t="str">
         <x:v>不属于CPU2共享故障；按CPU3程序版本确认</x:v>
       </x:c>
     </x:row>
@@ -45298,10 +46163,10 @@
         <x:v>历史</x:v>
       </x:c>
       <x:c r="B7" s="98" t="str">
-        <x:v>编号永久冻结</x:v>
+        <x:v>按CPU2版本归档</x:v>
       </x:c>
       <x:c r="C7" s="96" t="str">
-        <x:v>协议18及更早已使用编号不改作其他含义；删除或拆分后仍在对应CPU2历史页保留。</x:v>
+        <x:v>二代旧编号保留在对应CPU2历史页；后续版本可复用相同编号，但不得脱离CPU2程序版本解释。</x:v>
       </x:c>
       <x:c r="D7"/>
       <x:c r="E7"/>
@@ -45354,10 +46219,10 @@
         <x:v>发布</x:v>
       </x:c>
       <x:c r="B11" s="98" t="str">
-        <x:v>协议19待发布</x:v>
+        <x:v>协议23正式发布</x:v>
       </x:c>
       <x:c r="C11" s="96" t="str">
-        <x:v>当前源码已采用协议19编号；CPU2 V1.26.0.0仍使用协议18历史页，正式发布版本待发布阶段确认。</x:v>
+        <x:v>协议22开发态完成现行故障码重排，并随CPU2 V1.28.0.0 / CPU3 V1.26.0.0、共享协议23首次正式发布；CPU2 V1.27.0.0仍使用协议21历史页。</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
